--- a/趋势投资.xlsx
+++ b/趋势投资.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08.ubuntu_ws\ediedone.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9CE0A3-7C97-4524-A34D-E4F063ED0CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32961813-66EE-409A-B639-F4DA75F3DC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{AED13B3B-36B7-4FA7-B5AB-20EFD3D048A6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
   <si>
     <t>净值</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>腾讯控股D</t>
-  </si>
-  <si>
-    <t>腾讯控股F</t>
   </si>
   <si>
     <t>ETF</t>
@@ -560,7 +557,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -648,14 +645,20 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="22">
@@ -1117,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2F0F4F-0A39-42ED-82E1-F32DA41D3C99}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="17.3984375" style="4" customWidth="1"/>
@@ -1131,30 +1134,30 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1">
-        <v>2.843</v>
+        <v>2.6379999999999999</v>
       </c>
       <c r="B2" s="2">
-        <v>-5.4000000000000003E-3</v>
+        <v>-7.1999999999999995E-2</v>
       </c>
       <c r="C2" s="3">
-        <v>201.19</v>
-      </c>
-      <c r="D2" s="22">
-        <v>0.62839999999999996</v>
+        <v>169.89</v>
+      </c>
+      <c r="D2" s="28">
+        <v>0.52839999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1163,93 +1166,93 @@
       <c r="C3" s="11"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
+      <c r="A4" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="29">
-        <v>3.0310000000000001</v>
-      </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
+      <c r="B5" s="33">
+        <v>2.7909999999999999</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
       <c r="G5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="30">
-        <v>2.7799999999999998E-2</v>
-      </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
+      <c r="H5" s="29">
+        <v>-7.9299999999999995E-2</v>
+      </c>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="C6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="E6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="F6" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>44</v>
-      </c>
       <c r="G6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="I6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="J6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="16" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="28">
-        <v>4.1200000000000001E-2</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="32">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="19">
-        <v>2.06E-2</v>
+        <v>2.0199999999999999E-2</v>
       </c>
       <c r="E7" s="20">
         <v>84.490300000000005</v>
       </c>
       <c r="F7" s="18">
-        <v>49.87</v>
+        <v>45.39</v>
       </c>
       <c r="G7" s="21">
-        <f t="shared" ref="G7:G24" si="0">IF(E7&gt;0,F7/E7-1.0014,(F7-E7))</f>
-        <v>-0.4111547292411083</v>
+        <f t="shared" ref="G7:G23" si="0">IF(E7&gt;0,F7/E7-1.0014,(F7-E7))</f>
+        <v>-0.46417856748052744</v>
       </c>
       <c r="H7" s="20">
         <f>IF(E7&gt;0, IF(E7*1.25 &gt; F7,E7*1.25, IF(E7*1.25^2 &gt; F7,E7*1.25^2, IF(E7*1.25^3 &gt; F7,E7*1.25^3, IF(E7*1.25^4 &gt; F7,E7*1.25^4, IF(E7*1.25^5 &gt; F7,E7*1.25^5, IF(E7*1.25^6 &gt; F7,E7*1.25^6, IF(E7*1.25^7 &gt; F7, E7*1.25^7, IF(E7*1.25^8 &gt; F7, E7*1.25^8, IF(E7*1.25^9 &gt; F7, E7*1.25^9, E7*1.25^10))))))))),IF(1.25 &gt; F7-E7,1.25, IF(1.25^2 &gt; F7-E7,1.25^2, IF(1.25^3 &gt; F7-E7,1.25^3, IF(1.25^4 &gt; F7-E7,1.25^4, IF(1.25^5 &gt; F7-E7,1.25^5, IF(1.25^6 &gt; F7-E7,1.25^6, IF(1.25^7 &gt; F7-E7, 1.25^7, IF(1.25^8 &gt; F7-E7, 1.25^8, IF(1.25^9 &gt; F7-E7, 1.25^9, IF(1.25^10 &gt; F7-E7, 1.25^10, IF(1.25^11 &gt; F7-E7, 1.25^11, IF(1.25^12 &gt; F7-E7, 1.25^12, IF(1.25^13 &gt; F7-E7, 1.25^13, IF(1.25^14 &gt; F7-E7, 1.25^14, IF(1.25^15 &gt; F7-E7, 1.25^15, IF(1.25^16 &gt; F7-E7, 1.25^16, IF(1.25^17 &gt; F7-E7, 1.25^17, IF(1.25^18 &gt; F7-E7, 1.25^18, IF(1.25^19 &gt; F7-E7, 1.25^19, 1.25^20))))))))))))))))))))</f>
@@ -1264,30 +1267,30 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="27"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="27" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="19">
-        <v>1.14E-2</v>
+        <v>1.12E-2</v>
       </c>
       <c r="E8" s="20">
         <v>80.194000000000003</v>
       </c>
       <c r="F8" s="18">
-        <v>49.87</v>
+        <v>45.39</v>
       </c>
       <c r="G8" s="21">
         <f t="shared" si="0"/>
-        <v>-0.37953302740853445</v>
+        <v>-0.43539755592687746</v>
       </c>
       <c r="H8" s="20">
-        <f t="shared" ref="H8:H24" si="1">IF(E8&gt;0, IF(E8*1.25 &gt; F8,E8*1.25, IF(E8*1.25^2 &gt; F8,E8*1.25^2, IF(E8*1.25^3 &gt; F8,E8*1.25^3, IF(E8*1.25^4 &gt; F8,E8*1.25^4, IF(E8*1.25^5 &gt; F8,E8*1.25^5, IF(E8*1.25^6 &gt; F8,E8*1.25^6, IF(E8*1.25^7 &gt; F8, E8*1.25^7, IF(E8*1.25^8 &gt; F8, E8*1.25^8, IF(E8*1.25^9 &gt; F8, E8*1.25^9, E8*1.25^10))))))))),IF(1.25 &gt; F8-E8,1.25, IF(1.25^2 &gt; F8-E8,1.25^2, IF(1.25^3 &gt; F8-E8,1.25^3, IF(1.25^4 &gt; F8-E8,1.25^4, IF(1.25^5 &gt; F8-E8,1.25^5, IF(1.25^6 &gt; F8-E8,1.25^6, IF(1.25^7 &gt; F8-E8, 1.25^7, IF(1.25^8 &gt; F8-E8, 1.25^8, IF(1.25^9 &gt; F8-E8, 1.25^9, IF(1.25^10 &gt; F8-E8, 1.25^10, IF(1.25^11 &gt; F8-E8, 1.25^11, IF(1.25^12 &gt; F8-E8, 1.25^12, IF(1.25^13 &gt; F8-E8, 1.25^13, IF(1.25^14 &gt; F8-E8, 1.25^14, IF(1.25^15 &gt; F8-E8, 1.25^15, IF(1.25^16 &gt; F8-E8, 1.25^16, IF(1.25^17 &gt; F8-E8, 1.25^17, IF(1.25^18 &gt; F8-E8, 1.25^18, IF(1.25^19 &gt; F8-E8, 1.25^19, 1.25^20))))))))))))))))))))</f>
+        <f t="shared" ref="H8:H23" si="1">IF(E8&gt;0, IF(E8*1.25 &gt; F8,E8*1.25, IF(E8*1.25^2 &gt; F8,E8*1.25^2, IF(E8*1.25^3 &gt; F8,E8*1.25^3, IF(E8*1.25^4 &gt; F8,E8*1.25^4, IF(E8*1.25^5 &gt; F8,E8*1.25^5, IF(E8*1.25^6 &gt; F8,E8*1.25^6, IF(E8*1.25^7 &gt; F8, E8*1.25^7, IF(E8*1.25^8 &gt; F8, E8*1.25^8, IF(E8*1.25^9 &gt; F8, E8*1.25^9, E8*1.25^10))))))))),IF(1.25 &gt; F8-E8,1.25, IF(1.25^2 &gt; F8-E8,1.25^2, IF(1.25^3 &gt; F8-E8,1.25^3, IF(1.25^4 &gt; F8-E8,1.25^4, IF(1.25^5 &gt; F8-E8,1.25^5, IF(1.25^6 &gt; F8-E8,1.25^6, IF(1.25^7 &gt; F8-E8, 1.25^7, IF(1.25^8 &gt; F8-E8, 1.25^8, IF(1.25^9 &gt; F8-E8, 1.25^9, IF(1.25^10 &gt; F8-E8, 1.25^10, IF(1.25^11 &gt; F8-E8, 1.25^11, IF(1.25^12 &gt; F8-E8, 1.25^12, IF(1.25^13 &gt; F8-E8, 1.25^13, IF(1.25^14 &gt; F8-E8, 1.25^14, IF(1.25^15 &gt; F8-E8, 1.25^15, IF(1.25^16 &gt; F8-E8, 1.25^16, IF(1.25^17 &gt; F8-E8, 1.25^17, IF(1.25^18 &gt; F8-E8, 1.25^18, IF(1.25^19 &gt; F8-E8, 1.25^19, 1.25^20))))))))))))))))))))</f>
         <v>100.24250000000001</v>
       </c>
       <c r="I8" s="20">
-        <f t="shared" ref="I8:I24" si="2">H8/1.25*0.92</f>
+        <f t="shared" ref="I8:I23" si="2">H8/1.25*0.92</f>
         <v>73.778480000000002</v>
       </c>
       <c r="J8" s="20">
@@ -1295,23 +1298,23 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="6" t="s">
+      <c r="A9" s="30"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="27" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="19">
-        <v>9.1999999999999998E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="E9" s="20">
         <v>152.2038</v>
       </c>
       <c r="F9" s="18">
-        <v>49.87</v>
+        <v>45.39</v>
       </c>
       <c r="G9" s="21">
         <f t="shared" si="0"/>
-        <v>-0.67374720815117639</v>
+        <v>-0.70318142727054123</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="1"/>
@@ -1326,14 +1329,14 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="28">
-        <v>0.01</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>58</v>
+      <c r="B10" s="32">
+        <v>1.04E-2</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>57</v>
       </c>
       <c r="D10" s="19">
         <v>8.9999999999999998E-4</v>
@@ -1342,11 +1345,11 @@
         <v>8.8960000000000008</v>
       </c>
       <c r="F10" s="18">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="G10" s="21">
         <f t="shared" si="0"/>
-        <v>-0.93058165467625908</v>
+        <v>-0.93282985611510805</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="1"/>
@@ -1361,23 +1364,23 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="27" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="19">
-        <v>9.1000000000000004E-3</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="E11" s="20">
         <v>9.5820000000000007</v>
       </c>
       <c r="F11" s="18">
-        <v>9.1199999999999992</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="G11" s="21">
         <f t="shared" si="0"/>
-        <v>-4.9615403882279474E-2</v>
+        <v>-7.5705990398664436E-2</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="1"/>
@@ -1396,23 +1399,23 @@
         <v>8</v>
       </c>
       <c r="B12" s="22">
-        <v>6.1999999999999998E-3</v>
-      </c>
-      <c r="C12" s="6" t="s">
+        <v>6.3E-3</v>
+      </c>
+      <c r="C12" s="27" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="19">
-        <v>6.1999999999999998E-3</v>
+        <v>6.3E-3</v>
       </c>
       <c r="E12" s="20">
         <v>5.1760000000000002</v>
       </c>
       <c r="F12" s="18">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="G12" s="21">
         <f t="shared" si="0"/>
-        <v>-0.27690231839258128</v>
+        <v>-0.31554219474497691</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="1"/>
@@ -1427,58 +1430,58 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="28">
-        <v>0.36570000000000003</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="32">
+        <v>0.2651</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="19">
-        <v>0.1186</v>
+        <v>0.10970000000000001</v>
       </c>
       <c r="E13" s="20">
         <v>370</v>
       </c>
       <c r="F13" s="18">
-        <v>493.4</v>
+        <v>427.2</v>
       </c>
       <c r="G13" s="21">
         <f t="shared" si="0"/>
-        <v>0.33211351351351337</v>
+        <v>0.1531945945945945</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="1"/>
-        <v>578.125</v>
+        <v>462.5</v>
       </c>
       <c r="I13" s="20">
         <f t="shared" si="2"/>
-        <v>425.5</v>
+        <v>340.40000000000003</v>
       </c>
       <c r="J13" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="6" t="s">
+      <c r="A14" s="30"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="27" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="19">
-        <v>0.16800000000000001</v>
+        <v>0.15540000000000001</v>
       </c>
       <c r="E14" s="20">
         <v>330</v>
       </c>
       <c r="F14" s="18">
-        <v>493.4</v>
+        <v>427.2</v>
       </c>
       <c r="G14" s="21">
         <f t="shared" si="0"/>
-        <v>0.49375151515151505</v>
+        <v>0.29314545454545438</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="1"/>
@@ -1493,655 +1496,622 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="6" t="s">
+      <c r="A15" s="30" t="s">
         <v>13</v>
       </c>
+      <c r="B15" s="32">
+        <v>4.7100000000000003E-2</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>14</v>
+      </c>
       <c r="D15" s="19">
-        <v>7.9100000000000004E-2</v>
+        <v>3.4799999999999998E-2</v>
       </c>
       <c r="E15" s="20">
-        <v>370</v>
+        <v>1.3997999999999999</v>
       </c>
       <c r="F15" s="18">
-        <v>493.4</v>
+        <v>1.48</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="0"/>
-        <v>0.33211351351351337</v>
+        <v>5.5893899128447E-2</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="1"/>
-        <v>578.125</v>
+        <v>1.7497499999999999</v>
       </c>
       <c r="I15" s="20">
         <f t="shared" si="2"/>
-        <v>425.5</v>
+        <v>1.2878160000000001</v>
       </c>
       <c r="J15" s="20">
-        <v>425.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="28">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="A16" s="30"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="27" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="19">
-        <v>3.3500000000000002E-2</v>
+        <v>1.23E-2</v>
       </c>
       <c r="E16" s="20">
-        <v>1.3997999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="F16" s="18">
-        <v>1.5349999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="G16" s="21">
         <f t="shared" si="0"/>
-        <v>9.5185226460922978E-2</v>
+        <v>3.1933333333333369E-2</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="1"/>
-        <v>1.7497499999999999</v>
+        <v>0.75</v>
       </c>
       <c r="I16" s="20">
         <f t="shared" si="2"/>
-        <v>1.2878160000000001</v>
-      </c>
-      <c r="J16" s="20">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="J16" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="B17" s="22">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>17</v>
+      </c>
       <c r="D17" s="19">
-        <v>1.15E-2</v>
+        <v>1.3599999999999999E-2</v>
       </c>
       <c r="E17" s="20">
-        <v>0.6</v>
+        <v>52.684100000000001</v>
       </c>
       <c r="F17" s="18">
-        <v>0.628</v>
+        <v>25.07</v>
       </c>
       <c r="G17" s="21">
         <f t="shared" si="0"/>
-        <v>4.5266666666666566E-2</v>
+        <v>-0.52554485584834898</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>65.855125000000001</v>
       </c>
       <c r="I17" s="20">
         <f t="shared" si="2"/>
-        <v>0.55200000000000005</v>
-      </c>
-      <c r="J17" s="26">
+        <v>48.469372</v>
+      </c>
+      <c r="J17" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="22">
-        <v>1.3599999999999999E-2</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>18</v>
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>56</v>
       </c>
       <c r="D18" s="19">
-        <v>1.3599999999999999E-2</v>
+        <v>4.4200000000000003E-2</v>
       </c>
       <c r="E18" s="20">
-        <v>52.684100000000001</v>
+        <v>1.98</v>
       </c>
       <c r="F18" s="18">
-        <v>27.04</v>
+        <v>2.72</v>
       </c>
       <c r="G18" s="21">
         <f t="shared" si="0"/>
-        <v>-0.48815217000954758</v>
+        <v>0.37233737373737386</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="1"/>
-        <v>65.855125000000001</v>
+        <v>3.09375</v>
       </c>
       <c r="I18" s="20">
         <f t="shared" si="2"/>
-        <v>48.469372</v>
+        <v>2.2770000000000001</v>
       </c>
       <c r="J18" s="20">
-        <v>0</v>
+        <v>2.2770000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="22">
-        <v>4.19E-2</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>57</v>
+      <c r="B19" s="32">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>20</v>
       </c>
       <c r="D19" s="19">
-        <v>4.19E-2</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="E19" s="20">
-        <v>1.98</v>
+        <v>23.686</v>
       </c>
       <c r="F19" s="18">
-        <v>2.75</v>
+        <v>9.1</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="0"/>
-        <v>0.38748888888888877</v>
+        <v>-0.61720680570801323</v>
       </c>
       <c r="H19" s="20">
         <f t="shared" si="1"/>
-        <v>3.09375</v>
+        <v>29.607500000000002</v>
       </c>
       <c r="I19" s="20">
         <f t="shared" si="2"/>
-        <v>2.2770000000000001</v>
+        <v>21.791119999999999</v>
       </c>
       <c r="J19" s="20">
-        <v>2.2770000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="28">
-        <v>2.9899999999999999E-2</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="A20" s="30"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="27" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="19">
-        <v>1.5299999999999999E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E20" s="20">
-        <v>23.686</v>
+        <v>59.759799999999998</v>
       </c>
       <c r="F20" s="18">
-        <v>9.5500000000000007</v>
+        <v>80.849999999999994</v>
       </c>
       <c r="G20" s="21">
         <f t="shared" si="0"/>
-        <v>-0.59820824115511284</v>
+        <v>0.35151617441825422</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" si="1"/>
-        <v>29.607500000000002</v>
+        <v>93.374687499999993</v>
       </c>
       <c r="I20" s="20">
         <f t="shared" si="2"/>
-        <v>21.791119999999999</v>
+        <v>68.723770000000002</v>
       </c>
       <c r="J20" s="20">
-        <v>0</v>
+        <v>68.724000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="B21" s="22">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>23</v>
+      </c>
       <c r="D21" s="19">
-        <v>1.46E-2</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="E21" s="20">
-        <v>59.759799999999998</v>
+        <v>5.5410000000000004</v>
       </c>
       <c r="F21" s="18">
-        <v>79.66</v>
+        <v>1.91</v>
       </c>
       <c r="G21" s="21">
         <f t="shared" si="0"/>
-        <v>0.33160312250040991</v>
+        <v>-0.65669687781988828</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="1"/>
-        <v>93.374687499999993</v>
+        <v>6.9262500000000005</v>
       </c>
       <c r="I21" s="20">
         <f t="shared" si="2"/>
-        <v>68.723770000000002</v>
+        <v>5.0977200000000007</v>
       </c>
       <c r="J21" s="20">
-        <v>68.724000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" s="22">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>24</v>
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>25</v>
       </c>
       <c r="D22" s="19">
-        <v>8.3000000000000001E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="E22" s="20">
-        <v>5.5410000000000004</v>
+        <v>28.935300000000002</v>
       </c>
       <c r="F22" s="18">
-        <v>2.08</v>
+        <v>13.89</v>
       </c>
       <c r="G22" s="21">
         <f t="shared" si="0"/>
-        <v>-0.62601649521746983</v>
+        <v>-0.52136350478481308</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="1"/>
-        <v>6.9262500000000005</v>
+        <v>36.169125000000001</v>
       </c>
       <c r="I22" s="20">
         <f t="shared" si="2"/>
-        <v>5.0977200000000007</v>
+        <v>26.620476000000004</v>
       </c>
       <c r="J22" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="5" t="s">
-        <v>25</v>
+      <c r="A23" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="B23" s="22">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>26</v>
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>27</v>
       </c>
       <c r="D23" s="19">
-        <v>4.0000000000000001E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="E23" s="20">
-        <v>28.935300000000002</v>
+        <v>6.117</v>
       </c>
       <c r="F23" s="18">
-        <v>17.39</v>
+        <v>2.64</v>
       </c>
       <c r="G23" s="21">
         <f t="shared" si="0"/>
-        <v>-0.40040398475218864</v>
+        <v>-0.56981589014222656</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="1"/>
-        <v>36.169125000000001</v>
+        <v>7.6462500000000002</v>
       </c>
       <c r="I23" s="20">
         <f t="shared" si="2"/>
-        <v>26.620476000000004</v>
+        <v>5.6276400000000004</v>
       </c>
       <c r="J23" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="22">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="19">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="E24" s="20">
-        <v>6.117</v>
-      </c>
-      <c r="F24" s="18">
-        <v>2.64</v>
-      </c>
-      <c r="G24" s="21">
-        <f t="shared" si="0"/>
-        <v>-0.56981589014222656</v>
-      </c>
-      <c r="H24" s="20">
-        <f t="shared" si="1"/>
-        <v>7.6462500000000002</v>
-      </c>
-      <c r="I24" s="20">
-        <f t="shared" si="2"/>
-        <v>5.6276400000000004</v>
-      </c>
-      <c r="J24" s="20">
+      <c r="A24" s="7"/>
+      <c r="B24" s="14"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13"/>
+      <c r="G24"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="16" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="7"/>
-      <c r="B25" s="14"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="G25"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
+      <c r="B26" s="33">
+        <v>2.206</v>
+      </c>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="29">
+        <v>-3.5999999999999997E-2</v>
+      </c>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="29">
-        <v>2.2879999999999998</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
+        <v>38</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>43</v>
+      </c>
       <c r="G27" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="30">
-        <v>-2.0999999999999999E-3</v>
-      </c>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
+        <v>45</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>49</v>
+        <v>28</v>
+      </c>
+      <c r="B28" s="19">
+        <v>1.44E-2</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="19">
+        <v>1.44E-2</v>
+      </c>
+      <c r="E28" s="23">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="F28" s="23">
+        <v>5.9</v>
+      </c>
+      <c r="G28" s="21">
+        <f t="shared" ref="G28:G32" si="3">IF(E28&gt;0,F28/E28-1.0014,(F28-E28))</f>
+        <v>-0.36562413793103443</v>
+      </c>
+      <c r="H28" s="20">
+        <f t="shared" ref="H28:H32" si="4">IF(E28&gt;0, IF(E28*1.25 &gt; F28,E28*1.25, IF(E28*1.25^2 &gt; F28,E28*1.25^2, IF(E28*1.25^3 &gt; F28,E28*1.25^3, IF(E28*1.25^4 &gt; F28,E28*1.25^4, IF(E28*1.25^5 &gt; F28,E28*1.25^5, IF(E28*1.25^6 &gt; F28,E28*1.25^6, IF(E28*1.25^7 &gt; F28, E28*1.25^7, IF(E28*1.25^8 &gt; F28, E28*1.25^8, IF(E28*1.25^9 &gt; F28, E28*1.25^9, E28*1.25^10))))))))),IF(1.25 &gt; F28-E28,1.25, IF(1.25^2 &gt; F28-E28,1.25^2, IF(1.25^3 &gt; F28-E28,1.25^3, IF(1.25^4 &gt; F28-E28,1.25^4, IF(1.25^5 &gt; F28-E28,1.25^5, IF(1.25^6 &gt; F28-E28,1.25^6, IF(1.25^7 &gt; F28-E28, 1.25^7, IF(1.25^8 &gt; F28-E28, 1.25^8, IF(1.25^9 &gt; F28-E28, 1.25^9, IF(1.25^10 &gt; F28-E28, 1.25^10, IF(1.25^11 &gt; F28-E28, 1.25^11, IF(1.25^12 &gt; F28-E28, 1.25^12, IF(1.25^13 &gt; F28-E28, 1.25^13, IF(1.25^14 &gt; F28-E28, 1.25^14, IF(1.25^15 &gt; F28-E28, 1.25^15, IF(1.25^16 &gt; F28-E28, 1.25^16, IF(1.25^17 &gt; F28-E28, 1.25^17, IF(1.25^18 &gt; F28-E28, 1.25^18, IF(1.25^19 &gt; F28-E28, 1.25^19, 1.25^20))))))))))))))))))))</f>
+        <v>11.6</v>
+      </c>
+      <c r="I28" s="20">
+        <f>H28/1.25*0.92</f>
+        <v>8.5375999999999994</v>
+      </c>
+      <c r="J28" s="20">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="19">
-        <v>1.41E-2</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>30</v>
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>31</v>
       </c>
       <c r="D29" s="19">
-        <v>1.41E-2</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="E29" s="23">
-        <v>9.2799999999999994</v>
+        <v>33.82</v>
       </c>
       <c r="F29" s="23">
-        <v>6.15</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="G29" s="21">
-        <f t="shared" ref="G29:G33" si="3">IF(E29&gt;0,F29/E29-1.0014,(F29-E29))</f>
-        <v>-0.33868448275862062</v>
+        <f t="shared" si="3"/>
+        <v>-0.48838994677705505</v>
       </c>
       <c r="H29" s="20">
-        <f t="shared" ref="H29:H33" si="4">IF(E29&gt;0, IF(E29*1.25 &gt; F29,E29*1.25, IF(E29*1.25^2 &gt; F29,E29*1.25^2, IF(E29*1.25^3 &gt; F29,E29*1.25^3, IF(E29*1.25^4 &gt; F29,E29*1.25^4, IF(E29*1.25^5 &gt; F29,E29*1.25^5, IF(E29*1.25^6 &gt; F29,E29*1.25^6, IF(E29*1.25^7 &gt; F29, E29*1.25^7, IF(E29*1.25^8 &gt; F29, E29*1.25^8, IF(E29*1.25^9 &gt; F29, E29*1.25^9, E29*1.25^10))))))))),IF(1.25 &gt; F29-E29,1.25, IF(1.25^2 &gt; F29-E29,1.25^2, IF(1.25^3 &gt; F29-E29,1.25^3, IF(1.25^4 &gt; F29-E29,1.25^4, IF(1.25^5 &gt; F29-E29,1.25^5, IF(1.25^6 &gt; F29-E29,1.25^6, IF(1.25^7 &gt; F29-E29, 1.25^7, IF(1.25^8 &gt; F29-E29, 1.25^8, IF(1.25^9 &gt; F29-E29, 1.25^9, IF(1.25^10 &gt; F29-E29, 1.25^10, IF(1.25^11 &gt; F29-E29, 1.25^11, IF(1.25^12 &gt; F29-E29, 1.25^12, IF(1.25^13 &gt; F29-E29, 1.25^13, IF(1.25^14 &gt; F29-E29, 1.25^14, IF(1.25^15 &gt; F29-E29, 1.25^15, IF(1.25^16 &gt; F29-E29, 1.25^16, IF(1.25^17 &gt; F29-E29, 1.25^17, IF(1.25^18 &gt; F29-E29, 1.25^18, IF(1.25^19 &gt; F29-E29, 1.25^19, 1.25^20))))))))))))))))))))</f>
-        <v>11.6</v>
+        <f t="shared" si="4"/>
+        <v>42.274999999999999</v>
       </c>
       <c r="I29" s="20">
-        <f>H29/1.25*0.92</f>
-        <v>8.5375999999999994</v>
+        <f t="shared" ref="I29:I32" si="5">H29/1.25*0.92</f>
+        <v>31.114400000000003</v>
       </c>
       <c r="J29" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="19">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>32</v>
+      <c r="A30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="24">
+        <v>7.6E-3</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>55</v>
       </c>
       <c r="D30" s="19">
-        <v>5.8999999999999999E-3</v>
+        <v>7.6E-3</v>
       </c>
       <c r="E30" s="23">
-        <v>33.82</v>
+        <v>22.58</v>
       </c>
       <c r="F30" s="23">
-        <v>22.31</v>
+        <v>26.76</v>
       </c>
       <c r="G30" s="21">
         <f t="shared" si="3"/>
-        <v>-0.34173116499112965</v>
+        <v>0.18371957484499557</v>
       </c>
       <c r="H30" s="20">
         <f t="shared" si="4"/>
-        <v>42.274999999999999</v>
+        <v>28.224999999999998</v>
       </c>
       <c r="I30" s="20">
-        <f t="shared" ref="I30:I33" si="5">H30/1.25*0.92</f>
-        <v>31.114400000000003</v>
+        <f t="shared" si="5"/>
+        <v>20.773599999999998</v>
       </c>
       <c r="J30" s="20">
-        <v>0</v>
+        <v>25.966999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="24">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>56</v>
+      <c r="A31" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="31">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>33</v>
       </c>
       <c r="D31" s="19">
-        <v>7.7000000000000002E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="E31" s="23">
-        <v>22.58</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="F31" s="23">
-        <v>28.88</v>
+        <v>32.619999999999997</v>
       </c>
       <c r="G31" s="21">
         <f t="shared" si="3"/>
-        <v>0.27760797165633311</v>
+        <v>-0.10277741046831967</v>
       </c>
       <c r="H31" s="20">
         <f t="shared" si="4"/>
-        <v>35.28125</v>
+        <v>45.375</v>
       </c>
       <c r="I31" s="20">
         <f t="shared" si="5"/>
-        <v>25.967000000000002</v>
-      </c>
-      <c r="J31" s="20">
-        <v>25.966999999999999</v>
-      </c>
+        <v>33.396000000000001</v>
+      </c>
+      <c r="J31" s="20"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="31">
-        <v>3.1699999999999999E-2</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>34</v>
+      <c r="A32" s="30"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="D32" s="19">
-        <v>6.9999999999999999E-4</v>
+        <v>2.7099999999999999E-2</v>
       </c>
       <c r="E32" s="23">
-        <v>36.299999999999997</v>
+        <v>111.03400000000001</v>
       </c>
       <c r="F32" s="23">
-        <v>36.14</v>
+        <v>55.21</v>
       </c>
       <c r="G32" s="21">
         <f t="shared" si="3"/>
-        <v>-5.8077134986225243E-3</v>
+        <v>-0.50416491885368453</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="4"/>
-        <v>45.375</v>
+        <v>138.79250000000002</v>
       </c>
       <c r="I32" s="20">
         <f t="shared" si="5"/>
-        <v>33.396000000000001</v>
+        <v>102.15128000000003</v>
       </c>
       <c r="J32" s="20">
-        <v>33.396000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="27"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="19">
-        <v>3.1E-2</v>
-      </c>
-      <c r="E33" s="23">
-        <v>111.03400000000001</v>
-      </c>
-      <c r="F33" s="23">
-        <v>67.38</v>
-      </c>
-      <c r="G33" s="21">
-        <f t="shared" si="3"/>
-        <v>-0.3945588522434571</v>
-      </c>
-      <c r="H33" s="20">
-        <f t="shared" si="4"/>
-        <v>138.79250000000002</v>
-      </c>
-      <c r="I33" s="20">
-        <f t="shared" si="5"/>
-        <v>102.15128000000003</v>
-      </c>
-      <c r="J33" s="20">
-        <v>0</v>
-      </c>
+      <c r="A33" s="8"/>
+      <c r="B33" s="25"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="8"/>
-      <c r="B34" s="25"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
+      <c r="A34" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
+      <c r="A35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="16">
+        <v>34</v>
+      </c>
+      <c r="B36" s="16">
         <v>154004.837</v>
       </c>
-      <c r="C37" s="17">
-        <f>A2*B37</f>
-        <v>437835.75159100001</v>
+      <c r="C36" s="17">
+        <f>A2*B36</f>
+        <v>406264.760006</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="F11">
@@ -2149,12 +2119,12 @@
       <formula>$J$11</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
+  <conditionalFormatting sqref="F30">
     <cfRule type="cellIs" dxfId="6" priority="15" stopIfTrue="1" operator="lessThan">
-      <formula>$J$31</formula>
+      <formula>$J$30</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G24 G29:G33">
+  <conditionalFormatting sqref="G28:G32 G7:G23">
     <cfRule type="cellIs" dxfId="5" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -2162,22 +2132,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H25">
+  <conditionalFormatting sqref="H7:H24">
     <cfRule type="cellIs" dxfId="3" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>E7*1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
+  <conditionalFormatting sqref="H28">
     <cfRule type="cellIs" dxfId="2" priority="6" stopIfTrue="1" operator="greaterThan">
-      <formula>E29*1.25</formula>
+      <formula>E28*1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H34">
+  <conditionalFormatting sqref="H29:H33">
     <cfRule type="cellIs" dxfId="1" priority="14" stopIfTrue="1" operator="greaterThan">
-      <formula>E30 * 1.25</formula>
+      <formula>E29 * 1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:J25 I29:J34">
+  <conditionalFormatting sqref="I28:J33 I7:J24">
     <cfRule type="cellIs" dxfId="0" priority="4" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/趋势投资.xlsx
+++ b/趋势投资.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08.ubuntu_ws\ediedone.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32961813-66EE-409A-B639-F4DA75F3DC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8CD000-9570-43C1-8912-0B2CEBB622D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{AED13B3B-36B7-4FA7-B5AB-20EFD3D048A6}"/>
   </bookViews>
@@ -645,20 +645,20 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="22">
@@ -1148,16 +1148,16 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1">
-        <v>2.6379999999999999</v>
+        <v>2.548</v>
       </c>
       <c r="B2" s="2">
-        <v>-7.1999999999999995E-2</v>
+        <v>-3.4099999999999998E-2</v>
       </c>
       <c r="C2" s="3">
-        <v>169.89</v>
+        <v>156.02000000000001</v>
       </c>
       <c r="D2" s="28">
-        <v>0.52839999999999998</v>
+        <v>0.50600000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1166,38 +1166,38 @@
       <c r="C3" s="11"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="33">
-        <v>2.7909999999999999</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
+      <c r="B5" s="30">
+        <v>2.673</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
       <c r="G5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="29">
-        <v>-7.9299999999999995E-2</v>
-      </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
+      <c r="H5" s="31">
+        <v>-4.2099999999999999E-2</v>
+      </c>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16" t="s">
@@ -1232,27 +1232,27 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="32">
-        <v>4.0399999999999998E-2</v>
+        <v>3.61E-2</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="19">
-        <v>2.0199999999999999E-2</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="E7" s="20">
         <v>84.490300000000005</v>
       </c>
       <c r="F7" s="18">
-        <v>45.39</v>
+        <v>39.22</v>
       </c>
       <c r="G7" s="21">
         <f t="shared" ref="G7:G23" si="0">IF(E7&gt;0,F7/E7-1.0014,(F7-E7))</f>
-        <v>-0.46417856748052744</v>
+        <v>-0.53720470184151325</v>
       </c>
       <c r="H7" s="20">
         <f>IF(E7&gt;0, IF(E7*1.25 &gt; F7,E7*1.25, IF(E7*1.25^2 &gt; F7,E7*1.25^2, IF(E7*1.25^3 &gt; F7,E7*1.25^3, IF(E7*1.25^4 &gt; F7,E7*1.25^4, IF(E7*1.25^5 &gt; F7,E7*1.25^5, IF(E7*1.25^6 &gt; F7,E7*1.25^6, IF(E7*1.25^7 &gt; F7, E7*1.25^7, IF(E7*1.25^8 &gt; F7, E7*1.25^8, IF(E7*1.25^9 &gt; F7, E7*1.25^9, E7*1.25^10))))))))),IF(1.25 &gt; F7-E7,1.25, IF(1.25^2 &gt; F7-E7,1.25^2, IF(1.25^3 &gt; F7-E7,1.25^3, IF(1.25^4 &gt; F7-E7,1.25^4, IF(1.25^5 &gt; F7-E7,1.25^5, IF(1.25^6 &gt; F7-E7,1.25^6, IF(1.25^7 &gt; F7-E7, 1.25^7, IF(1.25^8 &gt; F7-E7, 1.25^8, IF(1.25^9 &gt; F7-E7, 1.25^9, IF(1.25^10 &gt; F7-E7, 1.25^10, IF(1.25^11 &gt; F7-E7, 1.25^11, IF(1.25^12 &gt; F7-E7, 1.25^12, IF(1.25^13 &gt; F7-E7, 1.25^13, IF(1.25^14 &gt; F7-E7, 1.25^14, IF(1.25^15 &gt; F7-E7, 1.25^15, IF(1.25^16 &gt; F7-E7, 1.25^16, IF(1.25^17 &gt; F7-E7, 1.25^17, IF(1.25^18 &gt; F7-E7, 1.25^18, IF(1.25^19 &gt; F7-E7, 1.25^19, 1.25^20))))))))))))))))))))</f>
@@ -1267,23 +1267,23 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="30"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="32"/>
       <c r="C8" s="27" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="19">
-        <v>1.12E-2</v>
+        <v>0.01</v>
       </c>
       <c r="E8" s="20">
         <v>80.194000000000003</v>
       </c>
       <c r="F8" s="18">
-        <v>45.39</v>
+        <v>39.22</v>
       </c>
       <c r="G8" s="21">
         <f t="shared" si="0"/>
-        <v>-0.43539755592687746</v>
+        <v>-0.51233598024789895</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" ref="H8:H23" si="1">IF(E8&gt;0, IF(E8*1.25 &gt; F8,E8*1.25, IF(E8*1.25^2 &gt; F8,E8*1.25^2, IF(E8*1.25^3 &gt; F8,E8*1.25^3, IF(E8*1.25^4 &gt; F8,E8*1.25^4, IF(E8*1.25^5 &gt; F8,E8*1.25^5, IF(E8*1.25^6 &gt; F8,E8*1.25^6, IF(E8*1.25^7 &gt; F8, E8*1.25^7, IF(E8*1.25^8 &gt; F8, E8*1.25^8, IF(E8*1.25^9 &gt; F8, E8*1.25^9, E8*1.25^10))))))))),IF(1.25 &gt; F8-E8,1.25, IF(1.25^2 &gt; F8-E8,1.25^2, IF(1.25^3 &gt; F8-E8,1.25^3, IF(1.25^4 &gt; F8-E8,1.25^4, IF(1.25^5 &gt; F8-E8,1.25^5, IF(1.25^6 &gt; F8-E8,1.25^6, IF(1.25^7 &gt; F8-E8, 1.25^7, IF(1.25^8 &gt; F8-E8, 1.25^8, IF(1.25^9 &gt; F8-E8, 1.25^9, IF(1.25^10 &gt; F8-E8, 1.25^10, IF(1.25^11 &gt; F8-E8, 1.25^11, IF(1.25^12 &gt; F8-E8, 1.25^12, IF(1.25^13 &gt; F8-E8, 1.25^13, IF(1.25^14 &gt; F8-E8, 1.25^14, IF(1.25^15 &gt; F8-E8, 1.25^15, IF(1.25^16 &gt; F8-E8, 1.25^16, IF(1.25^17 &gt; F8-E8, 1.25^17, IF(1.25^18 &gt; F8-E8, 1.25^18, IF(1.25^19 &gt; F8-E8, 1.25^19, 1.25^20))))))))))))))))))))</f>
@@ -1298,23 +1298,23 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="30"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="32"/>
       <c r="C9" s="27" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="19">
-        <v>8.9999999999999993E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="E9" s="20">
         <v>152.2038</v>
       </c>
       <c r="F9" s="18">
-        <v>45.39</v>
+        <v>39.22</v>
       </c>
       <c r="G9" s="21">
         <f t="shared" si="0"/>
-        <v>-0.70318142727054123</v>
+        <v>-0.74371917994163095</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="1"/>
@@ -1329,27 +1329,27 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="29" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="32">
-        <v>1.04E-2</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>57</v>
       </c>
       <c r="D10" s="19">
-        <v>8.9999999999999998E-4</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="E10" s="20">
         <v>8.8960000000000008</v>
       </c>
       <c r="F10" s="18">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="G10" s="21">
         <f t="shared" si="0"/>
-        <v>-0.93282985611510805</v>
+        <v>-0.94069856115107919</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="1"/>
@@ -1364,23 +1364,23 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="30"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="32"/>
       <c r="C11" s="27" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="19">
-        <v>9.4999999999999998E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="E11" s="20">
         <v>9.5820000000000007</v>
       </c>
       <c r="F11" s="18">
-        <v>8.8699999999999992</v>
+        <v>6.41</v>
       </c>
       <c r="G11" s="21">
         <f t="shared" si="0"/>
-        <v>-7.5705990398664436E-2</v>
+        <v>-0.33243736171989158</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="1"/>
@@ -1399,23 +1399,23 @@
         <v>8</v>
       </c>
       <c r="B12" s="22">
-        <v>6.3E-3</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="19">
-        <v>6.3E-3</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="E12" s="20">
         <v>5.1760000000000002</v>
       </c>
       <c r="F12" s="18">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="G12" s="21">
         <f t="shared" si="0"/>
-        <v>-0.31554219474497691</v>
+        <v>-0.36577403400309128</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="1"/>
@@ -1430,27 +1430,27 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="29" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="32">
-        <v>0.2651</v>
+        <v>0.26529999999999998</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="19">
-        <v>0.10970000000000001</v>
+        <v>0.10979999999999999</v>
       </c>
       <c r="E13" s="20">
         <v>370</v>
       </c>
       <c r="F13" s="18">
-        <v>427.2</v>
+        <v>411.8</v>
       </c>
       <c r="G13" s="21">
         <f t="shared" si="0"/>
-        <v>0.1531945945945945</v>
+        <v>0.11157297297297286</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="1"/>
@@ -1465,58 +1465,58 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="30"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="32"/>
       <c r="C14" s="27" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="19">
-        <v>0.15540000000000001</v>
+        <v>0.1555</v>
       </c>
       <c r="E14" s="20">
         <v>330</v>
       </c>
       <c r="F14" s="18">
-        <v>427.2</v>
+        <v>411.8</v>
       </c>
       <c r="G14" s="21">
         <f t="shared" si="0"/>
-        <v>0.29314545454545438</v>
+        <v>0.24647878787878774</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="1"/>
-        <v>515.625</v>
+        <v>412.5</v>
       </c>
       <c r="I14" s="20">
         <f t="shared" si="2"/>
-        <v>379.5</v>
+        <v>303.60000000000002</v>
       </c>
       <c r="J14" s="20">
         <v>379.5</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="29" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="32">
-        <v>4.7100000000000003E-2</v>
+        <v>4.3700000000000003E-2</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="19">
-        <v>3.4799999999999998E-2</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="E15" s="20">
         <v>1.3997999999999999</v>
       </c>
       <c r="F15" s="18">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="0"/>
-        <v>5.5893899128447E-2</v>
+        <v>-4.4120388626946672E-2</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="1"/>
@@ -1531,23 +1531,23 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="30"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="32"/>
       <c r="C16" s="27" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="19">
-        <v>1.23E-2</v>
+        <v>1.11E-2</v>
       </c>
       <c r="E16" s="20">
         <v>0.6</v>
       </c>
       <c r="F16" s="18">
-        <v>0.62</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="G16" s="21">
         <f t="shared" si="0"/>
-        <v>3.1933333333333369E-2</v>
+        <v>-9.8066666666666635E-2</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="1"/>
@@ -1566,23 +1566,23 @@
         <v>16</v>
       </c>
       <c r="B17" s="22">
-        <v>1.3599999999999999E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="19">
-        <v>1.3599999999999999E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="E17" s="20">
         <v>52.684100000000001</v>
       </c>
       <c r="F17" s="18">
-        <v>25.07</v>
+        <v>23.2</v>
       </c>
       <c r="G17" s="21">
         <f t="shared" si="0"/>
-        <v>-0.52554485584834898</v>
+        <v>-0.56103943580700832</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="1"/>
@@ -1601,58 +1601,58 @@
         <v>18</v>
       </c>
       <c r="B18" s="22">
-        <v>4.4200000000000003E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>56</v>
       </c>
       <c r="D18" s="19">
-        <v>4.4200000000000003E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="E18" s="20">
         <v>1.98</v>
       </c>
       <c r="F18" s="18">
-        <v>2.72</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="G18" s="21">
         <f t="shared" si="0"/>
-        <v>0.37233737373737386</v>
+        <v>0.14001414141414115</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="1"/>
-        <v>3.09375</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="I18" s="20">
         <f t="shared" si="2"/>
-        <v>2.2770000000000001</v>
+        <v>1.8216000000000001</v>
       </c>
       <c r="J18" s="20">
         <v>2.2770000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="32">
-        <v>3.1600000000000003E-2</v>
+        <v>2.8799999999999999E-2</v>
       </c>
       <c r="C19" s="27" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="19">
-        <v>1.5599999999999999E-2</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="E19" s="20">
         <v>23.686</v>
       </c>
       <c r="F19" s="18">
-        <v>9.1</v>
+        <v>7.12</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="0"/>
-        <v>-0.61720680570801323</v>
+        <v>-0.70080048974077513</v>
       </c>
       <c r="H19" s="20">
         <f t="shared" si="1"/>
@@ -1667,23 +1667,23 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="30"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="32"/>
       <c r="C20" s="27" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="19">
-        <v>1.6E-2</v>
+        <v>1.61E-2</v>
       </c>
       <c r="E20" s="20">
         <v>59.759799999999998</v>
       </c>
       <c r="F20" s="18">
-        <v>80.849999999999994</v>
+        <v>78.55</v>
       </c>
       <c r="G20" s="21">
         <f t="shared" si="0"/>
-        <v>0.35151617441825422</v>
+        <v>0.31302876314847095</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" si="1"/>
@@ -1702,23 +1702,23 @@
         <v>22</v>
       </c>
       <c r="B21" s="22">
-        <v>8.2000000000000007E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="C21" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="19">
-        <v>8.2000000000000007E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="E21" s="20">
         <v>5.5410000000000004</v>
       </c>
       <c r="F21" s="18">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="G21" s="21">
         <f t="shared" si="0"/>
-        <v>-0.65669687781988828</v>
+        <v>-0.73971438368525544</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="1"/>
@@ -1737,23 +1737,23 @@
         <v>24</v>
       </c>
       <c r="B22" s="22">
-        <v>3.3999999999999998E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="C22" s="27" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="19">
-        <v>3.3999999999999998E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="E22" s="20">
         <v>28.935300000000002</v>
       </c>
       <c r="F22" s="18">
-        <v>13.89</v>
+        <v>12.67</v>
       </c>
       <c r="G22" s="21">
         <f t="shared" si="0"/>
-        <v>-0.52136350478481308</v>
+        <v>-0.5635265374818994</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="1"/>
@@ -1772,13 +1772,13 @@
         <v>26</v>
       </c>
       <c r="B23" s="22">
-        <v>3.3999999999999998E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="C23" s="27" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="19">
-        <v>3.3999999999999998E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="E23" s="20">
         <v>6.117</v>
@@ -1813,38 +1813,38 @@
       <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="33">
-        <v>2.206</v>
-      </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
+      <c r="B26" s="30">
+        <v>2.1749999999999998</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
       <c r="G26" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H26" s="29">
-        <v>-3.5999999999999997E-2</v>
-      </c>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
+      <c r="H26" s="31">
+        <v>-1.41E-2</v>
+      </c>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="16" t="s">
@@ -1883,23 +1883,23 @@
         <v>28</v>
       </c>
       <c r="B28" s="19">
-        <v>1.44E-2</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="19">
-        <v>1.44E-2</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="E28" s="23">
         <v>9.2799999999999994</v>
       </c>
       <c r="F28" s="23">
-        <v>5.9</v>
+        <v>5.59</v>
       </c>
       <c r="G28" s="21">
         <f t="shared" ref="G28:G32" si="3">IF(E28&gt;0,F28/E28-1.0014,(F28-E28))</f>
-        <v>-0.36562413793103443</v>
+        <v>-0.39902931034482758</v>
       </c>
       <c r="H28" s="20">
         <f t="shared" ref="H28:H32" si="4">IF(E28&gt;0, IF(E28*1.25 &gt; F28,E28*1.25, IF(E28*1.25^2 &gt; F28,E28*1.25^2, IF(E28*1.25^3 &gt; F28,E28*1.25^3, IF(E28*1.25^4 &gt; F28,E28*1.25^4, IF(E28*1.25^5 &gt; F28,E28*1.25^5, IF(E28*1.25^6 &gt; F28,E28*1.25^6, IF(E28*1.25^7 &gt; F28, E28*1.25^7, IF(E28*1.25^8 &gt; F28, E28*1.25^8, IF(E28*1.25^9 &gt; F28, E28*1.25^9, E28*1.25^10))))))))),IF(1.25 &gt; F28-E28,1.25, IF(1.25^2 &gt; F28-E28,1.25^2, IF(1.25^3 &gt; F28-E28,1.25^3, IF(1.25^4 &gt; F28-E28,1.25^4, IF(1.25^5 &gt; F28-E28,1.25^5, IF(1.25^6 &gt; F28-E28,1.25^6, IF(1.25^7 &gt; F28-E28, 1.25^7, IF(1.25^8 &gt; F28-E28, 1.25^8, IF(1.25^9 &gt; F28-E28, 1.25^9, IF(1.25^10 &gt; F28-E28, 1.25^10, IF(1.25^11 &gt; F28-E28, 1.25^11, IF(1.25^12 &gt; F28-E28, 1.25^12, IF(1.25^13 &gt; F28-E28, 1.25^13, IF(1.25^14 &gt; F28-E28, 1.25^14, IF(1.25^15 &gt; F28-E28, 1.25^15, IF(1.25^16 &gt; F28-E28, 1.25^16, IF(1.25^17 &gt; F28-E28, 1.25^17, IF(1.25^18 &gt; F28-E28, 1.25^18, IF(1.25^19 &gt; F28-E28, 1.25^19, 1.25^20))))))))))))))))))))</f>
@@ -1930,11 +1930,11 @@
         <v>33.82</v>
       </c>
       <c r="F29" s="23">
-        <v>17.350000000000001</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="G29" s="21">
         <f t="shared" si="3"/>
-        <v>-0.48838994677705505</v>
+        <v>-0.51174890597279732</v>
       </c>
       <c r="H29" s="20">
         <f t="shared" si="4"/>
@@ -1953,23 +1953,23 @@
         <v>58</v>
       </c>
       <c r="B30" s="24">
-        <v>7.6E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>55</v>
       </c>
       <c r="D30" s="19">
-        <v>7.6E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="E30" s="23">
         <v>22.58</v>
       </c>
       <c r="F30" s="23">
-        <v>26.76</v>
+        <v>23.97</v>
       </c>
       <c r="G30" s="21">
         <f t="shared" si="3"/>
-        <v>0.18371957484499557</v>
+        <v>6.0158901682905164E-2</v>
       </c>
       <c r="H30" s="20">
         <f t="shared" si="4"/>
@@ -1980,31 +1980,31 @@
         <v>20.773599999999998</v>
       </c>
       <c r="J30" s="20">
-        <v>25.966999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="31">
-        <v>2.7799999999999998E-2</v>
+      <c r="B31" s="33">
+        <v>2.76E-2</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>33</v>
       </c>
       <c r="D31" s="19">
-        <v>6.9999999999999999E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="E31" s="23">
         <v>36.299999999999997</v>
       </c>
       <c r="F31" s="23">
-        <v>32.619999999999997</v>
+        <v>29</v>
       </c>
       <c r="G31" s="21">
         <f t="shared" si="3"/>
-        <v>-0.10277741046831967</v>
+        <v>-0.20250192837465564</v>
       </c>
       <c r="H31" s="20">
         <f t="shared" si="4"/>
@@ -2017,23 +2017,23 @@
       <c r="J31" s="20"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="30"/>
-      <c r="B32" s="31"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="28" t="s">
         <v>54</v>
       </c>
       <c r="D32" s="19">
-        <v>2.7099999999999999E-2</v>
+        <v>2.7E-2</v>
       </c>
       <c r="E32" s="23">
         <v>111.03400000000001</v>
       </c>
       <c r="F32" s="23">
-        <v>55.21</v>
+        <v>52.8</v>
       </c>
       <c r="G32" s="21">
         <f t="shared" si="3"/>
-        <v>-0.50416491885368453</v>
+        <v>-0.52586998216762448</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="4"/>
@@ -2055,11 +2055,11 @@
       <c r="J33" s="13"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
@@ -2088,11 +2088,14 @@
       </c>
       <c r="C36" s="17">
         <f>A2*B36</f>
-        <v>406264.760006</v>
+        <v>392404.32467599999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="B5:F5"/>
@@ -2109,9 +2112,6 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="F11">
@@ -2124,7 +2124,7 @@
       <formula>$J$30</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28:G32 G7:G23">
+  <conditionalFormatting sqref="G7:G23 G28:G32">
     <cfRule type="cellIs" dxfId="5" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -2147,7 +2147,7 @@
       <formula>E29 * 1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I28:J33 I7:J24">
+  <conditionalFormatting sqref="I7:J24 I28:J33">
     <cfRule type="cellIs" dxfId="0" priority="4" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/趋势投资.xlsx
+++ b/趋势投资.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08.ubuntu_ws\ediedone.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8CD000-9570-43C1-8912-0B2CEBB622D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44387B60-F8EF-4007-B05E-E96EB4EEA4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{AED13B3B-36B7-4FA7-B5AB-20EFD3D048A6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
   <si>
     <t>净值</t>
   </si>
@@ -47,12 +47,6 @@
     <t>食品饮料</t>
   </si>
   <si>
-    <t>洋河股份F</t>
-  </si>
-  <si>
-    <t>洋河股份L</t>
-  </si>
-  <si>
     <t>洋河股份D</t>
   </si>
   <si>
@@ -71,21 +65,9 @@
     <t>软件服务</t>
   </si>
   <si>
-    <t>腾讯控股L</t>
-  </si>
-  <si>
     <t>腾讯控股D</t>
   </si>
   <si>
-    <t>ETF</t>
-  </si>
-  <si>
-    <t>恒生ETF</t>
-  </si>
-  <si>
-    <t>恒指科技ETF</t>
-  </si>
-  <si>
     <t>交通运输</t>
   </si>
   <si>
@@ -98,9 +80,6 @@
     <t>家用电器</t>
   </si>
   <si>
-    <t>思摩尔国际</t>
-  </si>
-  <si>
     <t>美的集团</t>
   </si>
   <si>
@@ -110,12 +89,6 @@
     <t>澳博控股</t>
   </si>
   <si>
-    <t>电力设备</t>
-  </si>
-  <si>
-    <t>降基绿能</t>
-  </si>
-  <si>
     <t>港股抄作业</t>
   </si>
   <si>
@@ -126,12 +99,6 @@
   </si>
   <si>
     <t>挚文集团</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 通讯业务</t>
-  </si>
-  <si>
-    <t>哔哩哔哩</t>
   </si>
   <si>
     <t>食物饮品</t>
@@ -217,6 +184,10 @@
   </si>
   <si>
     <t>ETF</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>洋河股份F</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -228,7 +199,7 @@
     <numFmt numFmtId="176" formatCode="0.000"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,14 +362,6 @@
       <color theme="1"/>
       <name val="Liberation Sans"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="1"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -450,7 +413,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -488,6 +451,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -557,7 +570,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -624,21 +637,12 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -646,6 +650,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -654,11 +661,29 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="22">
@@ -1120,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2F0F4F-0A39-42ED-82E1-F32DA41D3C99}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="17.3984375" style="4" customWidth="1"/>
@@ -1134,30 +1159,30 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="16" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1">
-        <v>2.548</v>
+        <v>2.6760000000000002</v>
       </c>
       <c r="B2" s="2">
-        <v>-3.4099999999999998E-2</v>
+        <v>5.0200000000000002E-2</v>
       </c>
       <c r="C2" s="3">
-        <v>156.02000000000001</v>
-      </c>
-      <c r="D2" s="28">
-        <v>0.50600000000000001</v>
+        <v>171.52</v>
+      </c>
+      <c r="D2" s="25">
+        <v>0.4052</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1166,93 +1191,93 @@
       <c r="C3" s="11"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
+      <c r="A4" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="30">
-        <v>2.673</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="B5" s="28">
+        <v>2.8439999999999999</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
       <c r="G5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="31">
-        <v>-4.2099999999999999E-2</v>
-      </c>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
+      <c r="H5" s="29">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J6" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="27">
+        <v>3.15E-2</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="32">
-        <v>3.61E-2</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>3</v>
-      </c>
       <c r="D7" s="19">
-        <v>1.8100000000000002E-2</v>
+        <v>2.18E-2</v>
       </c>
       <c r="E7" s="20">
         <v>84.490300000000005</v>
       </c>
       <c r="F7" s="18">
-        <v>39.22</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="G7" s="21">
-        <f t="shared" ref="G7:G23" si="0">IF(E7&gt;0,F7/E7-1.0014,(F7-E7))</f>
-        <v>-0.53720470184151325</v>
+        <f t="shared" ref="G7:G17" si="0">IF(E7&gt;0,F7/E7-1.0014,(F7-E7))</f>
+        <v>-0.53578442046010022</v>
       </c>
       <c r="H7" s="20">
         <f>IF(E7&gt;0, IF(E7*1.25 &gt; F7,E7*1.25, IF(E7*1.25^2 &gt; F7,E7*1.25^2, IF(E7*1.25^3 &gt; F7,E7*1.25^3, IF(E7*1.25^4 &gt; F7,E7*1.25^4, IF(E7*1.25^5 &gt; F7,E7*1.25^5, IF(E7*1.25^6 &gt; F7,E7*1.25^6, IF(E7*1.25^7 &gt; F7, E7*1.25^7, IF(E7*1.25^8 &gt; F7, E7*1.25^8, IF(E7*1.25^9 &gt; F7, E7*1.25^9, E7*1.25^10))))))))),IF(1.25 &gt; F7-E7,1.25, IF(1.25^2 &gt; F7-E7,1.25^2, IF(1.25^3 &gt; F7-E7,1.25^3, IF(1.25^4 &gt; F7-E7,1.25^4, IF(1.25^5 &gt; F7-E7,1.25^5, IF(1.25^6 &gt; F7-E7,1.25^6, IF(1.25^7 &gt; F7-E7, 1.25^7, IF(1.25^8 &gt; F7-E7, 1.25^8, IF(1.25^9 &gt; F7-E7, 1.25^9, IF(1.25^10 &gt; F7-E7, 1.25^10, IF(1.25^11 &gt; F7-E7, 1.25^11, IF(1.25^12 &gt; F7-E7, 1.25^12, IF(1.25^13 &gt; F7-E7, 1.25^13, IF(1.25^14 &gt; F7-E7, 1.25^14, IF(1.25^15 &gt; F7-E7, 1.25^15, IF(1.25^16 &gt; F7-E7, 1.25^16, IF(1.25^17 &gt; F7-E7, 1.25^17, IF(1.25^18 &gt; F7-E7, 1.25^18, IF(1.25^19 &gt; F7-E7, 1.25^19, 1.25^20))))))))))))))))))))</f>
@@ -1267,864 +1292,629 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="29"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="27" t="s">
-        <v>4</v>
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="24" t="s">
+        <v>3</v>
       </c>
       <c r="D8" s="19">
-        <v>0.01</v>
+        <v>9.7000000000000003E-3</v>
       </c>
       <c r="E8" s="20">
-        <v>80.194000000000003</v>
+        <v>152.2038</v>
       </c>
       <c r="F8" s="18">
-        <v>39.22</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="G8" s="21">
         <f t="shared" si="0"/>
-        <v>-0.51233598024789895</v>
+        <v>-0.74293076335807651</v>
       </c>
       <c r="H8" s="20">
-        <f t="shared" ref="H8:H23" si="1">IF(E8&gt;0, IF(E8*1.25 &gt; F8,E8*1.25, IF(E8*1.25^2 &gt; F8,E8*1.25^2, IF(E8*1.25^3 &gt; F8,E8*1.25^3, IF(E8*1.25^4 &gt; F8,E8*1.25^4, IF(E8*1.25^5 &gt; F8,E8*1.25^5, IF(E8*1.25^6 &gt; F8,E8*1.25^6, IF(E8*1.25^7 &gt; F8, E8*1.25^7, IF(E8*1.25^8 &gt; F8, E8*1.25^8, IF(E8*1.25^9 &gt; F8, E8*1.25^9, E8*1.25^10))))))))),IF(1.25 &gt; F8-E8,1.25, IF(1.25^2 &gt; F8-E8,1.25^2, IF(1.25^3 &gt; F8-E8,1.25^3, IF(1.25^4 &gt; F8-E8,1.25^4, IF(1.25^5 &gt; F8-E8,1.25^5, IF(1.25^6 &gt; F8-E8,1.25^6, IF(1.25^7 &gt; F8-E8, 1.25^7, IF(1.25^8 &gt; F8-E8, 1.25^8, IF(1.25^9 &gt; F8-E8, 1.25^9, IF(1.25^10 &gt; F8-E8, 1.25^10, IF(1.25^11 &gt; F8-E8, 1.25^11, IF(1.25^12 &gt; F8-E8, 1.25^12, IF(1.25^13 &gt; F8-E8, 1.25^13, IF(1.25^14 &gt; F8-E8, 1.25^14, IF(1.25^15 &gt; F8-E8, 1.25^15, IF(1.25^16 &gt; F8-E8, 1.25^16, IF(1.25^17 &gt; F8-E8, 1.25^17, IF(1.25^18 &gt; F8-E8, 1.25^18, IF(1.25^19 &gt; F8-E8, 1.25^19, 1.25^20))))))))))))))))))))</f>
-        <v>100.24250000000001</v>
+        <f t="shared" ref="H8:H17" si="1">IF(E8&gt;0, IF(E8*1.25 &gt; F8,E8*1.25, IF(E8*1.25^2 &gt; F8,E8*1.25^2, IF(E8*1.25^3 &gt; F8,E8*1.25^3, IF(E8*1.25^4 &gt; F8,E8*1.25^4, IF(E8*1.25^5 &gt; F8,E8*1.25^5, IF(E8*1.25^6 &gt; F8,E8*1.25^6, IF(E8*1.25^7 &gt; F8, E8*1.25^7, IF(E8*1.25^8 &gt; F8, E8*1.25^8, IF(E8*1.25^9 &gt; F8, E8*1.25^9, E8*1.25^10))))))))),IF(1.25 &gt; F8-E8,1.25, IF(1.25^2 &gt; F8-E8,1.25^2, IF(1.25^3 &gt; F8-E8,1.25^3, IF(1.25^4 &gt; F8-E8,1.25^4, IF(1.25^5 &gt; F8-E8,1.25^5, IF(1.25^6 &gt; F8-E8,1.25^6, IF(1.25^7 &gt; F8-E8, 1.25^7, IF(1.25^8 &gt; F8-E8, 1.25^8, IF(1.25^9 &gt; F8-E8, 1.25^9, IF(1.25^10 &gt; F8-E8, 1.25^10, IF(1.25^11 &gt; F8-E8, 1.25^11, IF(1.25^12 &gt; F8-E8, 1.25^12, IF(1.25^13 &gt; F8-E8, 1.25^13, IF(1.25^14 &gt; F8-E8, 1.25^14, IF(1.25^15 &gt; F8-E8, 1.25^15, IF(1.25^16 &gt; F8-E8, 1.25^16, IF(1.25^17 &gt; F8-E8, 1.25^17, IF(1.25^18 &gt; F8-E8, 1.25^18, IF(1.25^19 &gt; F8-E8, 1.25^19, 1.25^20))))))))))))))))))))</f>
+        <v>190.25475</v>
       </c>
       <c r="I8" s="20">
-        <f t="shared" ref="I8:I23" si="2">H8/1.25*0.92</f>
-        <v>73.778480000000002</v>
+        <f t="shared" ref="I8:I17" si="2">H8/1.25*0.92</f>
+        <v>140.02749600000001</v>
       </c>
       <c r="J8" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="29"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="27" t="s">
-        <v>5</v>
+      <c r="A9" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="27">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="D9" s="19">
-        <v>8.0000000000000002E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="E9" s="20">
-        <v>152.2038</v>
+        <v>8.8960000000000008</v>
       </c>
       <c r="F9" s="18">
-        <v>39.22</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="G9" s="21">
         <f t="shared" si="0"/>
-        <v>-0.74371917994163095</v>
+        <v>-0.94800521582733821</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="1"/>
-        <v>190.25475</v>
+        <v>11.120000000000001</v>
       </c>
       <c r="I9" s="20">
         <f t="shared" si="2"/>
-        <v>140.02749600000001</v>
+        <v>8.1843200000000014</v>
       </c>
       <c r="J9" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="32">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>57</v>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="24" t="s">
+        <v>5</v>
       </c>
       <c r="D10" s="19">
-        <v>8.0000000000000004E-4</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="E10" s="20">
-        <v>8.8960000000000008</v>
+        <v>9.5820000000000007</v>
       </c>
       <c r="F10" s="18">
-        <v>0.54</v>
+        <v>7</v>
       </c>
       <c r="G10" s="21">
         <f t="shared" si="0"/>
-        <v>-0.94069856115107919</v>
+        <v>-0.27086357754122325</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="1"/>
-        <v>11.120000000000001</v>
+        <v>11.977500000000001</v>
       </c>
       <c r="I10" s="20">
         <f t="shared" si="2"/>
-        <v>8.1843200000000014</v>
+        <v>8.8154400000000006</v>
       </c>
       <c r="J10" s="20">
-        <v>0</v>
+        <v>8.8149999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="29"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="27" t="s">
+      <c r="A11" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="25">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="19">
-        <v>7.1000000000000004E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="E11" s="20">
-        <v>9.5820000000000007</v>
+        <v>5.1760000000000002</v>
       </c>
       <c r="F11" s="18">
-        <v>6.41</v>
+        <v>3.5</v>
       </c>
       <c r="G11" s="21">
         <f t="shared" si="0"/>
-        <v>-0.33243736171989158</v>
+        <v>-0.32520216383307587</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="1"/>
-        <v>11.977500000000001</v>
+        <v>6.4700000000000006</v>
       </c>
       <c r="I11" s="20">
         <f t="shared" si="2"/>
-        <v>8.8154400000000006</v>
+        <v>4.7619199999999999</v>
       </c>
       <c r="J11" s="20">
-        <v>8.8149999999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="22">
-        <v>6.1000000000000004E-3</v>
-      </c>
-      <c r="C12" s="27" t="s">
+      <c r="B12" s="37">
+        <v>0.19670000000000001</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="19">
-        <v>6.1000000000000004E-3</v>
+        <v>0.19670000000000001</v>
       </c>
       <c r="E12" s="20">
-        <v>5.1760000000000002</v>
+        <v>330</v>
       </c>
       <c r="F12" s="18">
-        <v>3.29</v>
+        <v>434.6</v>
       </c>
       <c r="G12" s="21">
         <f t="shared" si="0"/>
-        <v>-0.36577403400309128</v>
+        <v>0.31556969696969706</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="1"/>
-        <v>6.4700000000000006</v>
+        <v>515.625</v>
       </c>
       <c r="I12" s="20">
         <f t="shared" si="2"/>
-        <v>4.7619199999999999</v>
+        <v>379.5</v>
       </c>
       <c r="J12" s="20">
-        <v>0</v>
+        <v>379.5</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="32">
-        <v>0.26529999999999998</v>
-      </c>
-      <c r="C13" s="27" t="s">
+      <c r="B13" s="25">
+        <v>1.61E-2</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="19">
-        <v>0.10979999999999999</v>
+        <v>1.61E-2</v>
       </c>
       <c r="E13" s="20">
-        <v>370</v>
+        <v>52.684100000000001</v>
       </c>
       <c r="F13" s="18">
-        <v>411.8</v>
+        <v>23.7</v>
       </c>
       <c r="G13" s="21">
         <f t="shared" si="0"/>
-        <v>0.11157297297297286</v>
+        <v>-0.55154890640629728</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="1"/>
-        <v>462.5</v>
+        <v>65.855125000000001</v>
       </c>
       <c r="I13" s="20">
         <f t="shared" si="2"/>
-        <v>340.40000000000003</v>
+        <v>48.469372</v>
       </c>
       <c r="J13" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="29"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="27" t="s">
+      <c r="A14" s="24" t="s">
         <v>12</v>
       </c>
+      <c r="B14" s="25">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>45</v>
+      </c>
       <c r="D14" s="19">
-        <v>0.1555</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="E14" s="20">
-        <v>330</v>
+        <v>1.98</v>
       </c>
       <c r="F14" s="18">
-        <v>411.8</v>
+        <v>2.35</v>
       </c>
       <c r="G14" s="21">
         <f t="shared" si="0"/>
-        <v>0.24647878787878774</v>
+        <v>0.18546868686868678</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="1"/>
-        <v>412.5</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="I14" s="20">
         <f t="shared" si="2"/>
-        <v>303.60000000000002</v>
+        <v>1.8216000000000001</v>
       </c>
       <c r="J14" s="20">
-        <v>379.5</v>
+        <v>2.2770000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="32">
-        <v>4.3700000000000003E-2</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="25">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="19">
-        <v>3.2599999999999997E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="E15" s="20">
-        <v>1.3997999999999999</v>
+        <v>55.959800000000001</v>
       </c>
       <c r="F15" s="18">
-        <v>1.34</v>
+        <v>84.5</v>
       </c>
       <c r="G15" s="21">
         <f t="shared" si="0"/>
-        <v>-4.4120388626946672E-2</v>
+        <v>0.50861254471960216</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="1"/>
-        <v>1.7497499999999999</v>
+        <v>87.437187500000007</v>
       </c>
       <c r="I15" s="20">
         <f t="shared" si="2"/>
-        <v>1.2878160000000001</v>
+        <v>64.353770000000011</v>
       </c>
       <c r="J15" s="20">
-        <v>0</v>
+        <v>68.724000000000004</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="29"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="27" t="s">
+      <c r="A16" s="24" t="s">
         <v>15</v>
       </c>
+      <c r="B16" s="25">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>16</v>
+      </c>
       <c r="D16" s="19">
-        <v>1.11E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="E16" s="20">
-        <v>0.6</v>
+        <v>5.5410000000000004</v>
       </c>
       <c r="F16" s="18">
-        <v>0.54200000000000004</v>
+        <v>1.5</v>
       </c>
       <c r="G16" s="21">
         <f t="shared" si="0"/>
-        <v>-9.8066666666666635E-2</v>
+        <v>-0.73069074174336768</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>6.9262500000000005</v>
       </c>
       <c r="I16" s="20">
         <f t="shared" si="2"/>
-        <v>0.55200000000000005</v>
-      </c>
-      <c r="J16" s="26">
+        <v>5.0977200000000007</v>
+      </c>
+      <c r="J16" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="22">
-        <v>1.3100000000000001E-2</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="A17" s="16" t="s">
         <v>17</v>
       </c>
+      <c r="B17" s="25">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>18</v>
+      </c>
       <c r="D17" s="19">
-        <v>1.3100000000000001E-2</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="E17" s="20">
-        <v>52.684100000000001</v>
+        <v>6.117</v>
       </c>
       <c r="F17" s="18">
-        <v>23.2</v>
+        <v>2.64</v>
       </c>
       <c r="G17" s="21">
         <f t="shared" si="0"/>
-        <v>-0.56103943580700832</v>
+        <v>-0.56981589014222656</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="1"/>
-        <v>65.855125000000001</v>
+        <v>7.6462500000000002</v>
       </c>
       <c r="I17" s="20">
         <f t="shared" si="2"/>
-        <v>48.469372</v>
+        <v>5.6276400000000004</v>
       </c>
       <c r="J17" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="22">
-        <v>3.8100000000000002E-2</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="19">
-        <v>3.8100000000000002E-2</v>
-      </c>
-      <c r="E18" s="20">
-        <v>1.98</v>
-      </c>
-      <c r="F18" s="18">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="G18" s="21">
-        <f t="shared" si="0"/>
-        <v>0.14001414141414115</v>
-      </c>
-      <c r="H18" s="20">
-        <f t="shared" si="1"/>
-        <v>2.4750000000000001</v>
-      </c>
-      <c r="I18" s="20">
-        <f t="shared" si="2"/>
-        <v>1.8216000000000001</v>
-      </c>
-      <c r="J18" s="20">
-        <v>2.2770000000000001</v>
-      </c>
+      <c r="A18" s="7"/>
+      <c r="B18" s="14"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="G18"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="32"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="33">
+        <v>2.2240000000000002</v>
+      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="29">
+        <v>2.23E-2</v>
+      </c>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="32">
-        <v>2.8799999999999999E-2</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="B22" s="25">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="19">
-        <v>1.2699999999999999E-2</v>
-      </c>
-      <c r="E19" s="20">
-        <v>23.686</v>
-      </c>
-      <c r="F19" s="18">
-        <v>7.12</v>
-      </c>
-      <c r="G19" s="21">
-        <f t="shared" si="0"/>
-        <v>-0.70080048974077513</v>
-      </c>
-      <c r="H19" s="20">
-        <f t="shared" si="1"/>
-        <v>29.607500000000002</v>
-      </c>
-      <c r="I19" s="20">
-        <f t="shared" si="2"/>
-        <v>21.791119999999999</v>
-      </c>
-      <c r="J19" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="29"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="19">
-        <v>1.61E-2</v>
-      </c>
-      <c r="E20" s="20">
-        <v>59.759799999999998</v>
-      </c>
-      <c r="F20" s="18">
-        <v>78.55</v>
-      </c>
-      <c r="G20" s="21">
-        <f t="shared" si="0"/>
-        <v>0.31302876314847095</v>
-      </c>
-      <c r="H20" s="20">
-        <f t="shared" si="1"/>
-        <v>93.374687499999993</v>
-      </c>
-      <c r="I20" s="20">
-        <f t="shared" si="2"/>
-        <v>68.723770000000002</v>
-      </c>
-      <c r="J20" s="20">
-        <v>68.724000000000004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="22">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="19">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="E21" s="20">
-        <v>5.5410000000000004</v>
-      </c>
-      <c r="F21" s="18">
-        <v>1.45</v>
-      </c>
-      <c r="G21" s="21">
-        <f t="shared" si="0"/>
-        <v>-0.73971438368525544</v>
-      </c>
-      <c r="H21" s="20">
-        <f t="shared" si="1"/>
-        <v>6.9262500000000005</v>
-      </c>
-      <c r="I21" s="20">
-        <f t="shared" si="2"/>
-        <v>5.0977200000000007</v>
-      </c>
-      <c r="J21" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="22">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>25</v>
-      </c>
       <c r="D22" s="19">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="E22" s="20">
-        <v>28.935300000000002</v>
-      </c>
-      <c r="F22" s="18">
-        <v>12.67</v>
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="E22" s="22">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="F22" s="22">
+        <v>5.88</v>
       </c>
       <c r="G22" s="21">
-        <f t="shared" si="0"/>
-        <v>-0.5635265374818994</v>
+        <f t="shared" ref="G22:G25" si="3">IF(E22&gt;0,F22/E22-1.0014,(F22-E22))</f>
+        <v>-0.36777931034482758</v>
       </c>
       <c r="H22" s="20">
-        <f t="shared" si="1"/>
-        <v>36.169125000000001</v>
+        <f t="shared" ref="H22:H25" si="4">IF(E22&gt;0, IF(E22*1.25 &gt; F22,E22*1.25, IF(E22*1.25^2 &gt; F22,E22*1.25^2, IF(E22*1.25^3 &gt; F22,E22*1.25^3, IF(E22*1.25^4 &gt; F22,E22*1.25^4, IF(E22*1.25^5 &gt; F22,E22*1.25^5, IF(E22*1.25^6 &gt; F22,E22*1.25^6, IF(E22*1.25^7 &gt; F22, E22*1.25^7, IF(E22*1.25^8 &gt; F22, E22*1.25^8, IF(E22*1.25^9 &gt; F22, E22*1.25^9, E22*1.25^10))))))))),IF(1.25 &gt; F22-E22,1.25, IF(1.25^2 &gt; F22-E22,1.25^2, IF(1.25^3 &gt; F22-E22,1.25^3, IF(1.25^4 &gt; F22-E22,1.25^4, IF(1.25^5 &gt; F22-E22,1.25^5, IF(1.25^6 &gt; F22-E22,1.25^6, IF(1.25^7 &gt; F22-E22, 1.25^7, IF(1.25^8 &gt; F22-E22, 1.25^8, IF(1.25^9 &gt; F22-E22, 1.25^9, IF(1.25^10 &gt; F22-E22, 1.25^10, IF(1.25^11 &gt; F22-E22, 1.25^11, IF(1.25^12 &gt; F22-E22, 1.25^12, IF(1.25^13 &gt; F22-E22, 1.25^13, IF(1.25^14 &gt; F22-E22, 1.25^14, IF(1.25^15 &gt; F22-E22, 1.25^15, IF(1.25^16 &gt; F22-E22, 1.25^16, IF(1.25^17 &gt; F22-E22, 1.25^17, IF(1.25^18 &gt; F22-E22, 1.25^18, IF(1.25^19 &gt; F22-E22, 1.25^19, 1.25^20))))))))))))))))))))</f>
+        <v>11.6</v>
       </c>
       <c r="I22" s="20">
-        <f t="shared" si="2"/>
-        <v>26.620476000000004</v>
+        <f>H22/1.25*0.92</f>
+        <v>8.5375999999999994</v>
       </c>
       <c r="J22" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="22">
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>27</v>
+      <c r="A23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="25">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="D23" s="19">
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="E23" s="20">
-        <v>6.117</v>
-      </c>
-      <c r="F23" s="18">
-        <v>2.64</v>
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="E23" s="22">
+        <v>22.58</v>
+      </c>
+      <c r="F23" s="22">
+        <v>26.24</v>
       </c>
       <c r="G23" s="21">
-        <f t="shared" si="0"/>
-        <v>-0.56981589014222656</v>
+        <f t="shared" si="3"/>
+        <v>0.16069034543844096</v>
       </c>
       <c r="H23" s="20">
-        <f t="shared" si="1"/>
-        <v>7.6462500000000002</v>
+        <f t="shared" si="4"/>
+        <v>28.224999999999998</v>
       </c>
       <c r="I23" s="20">
-        <f t="shared" si="2"/>
-        <v>5.6276400000000004</v>
+        <f t="shared" ref="I23:I25" si="5">H23/1.25*0.92</f>
+        <v>20.773599999999998</v>
       </c>
       <c r="J23" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="7"/>
-      <c r="B24" s="14"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13"/>
-      <c r="G24"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
+      <c r="A24" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="27">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="19">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="E24" s="22">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="F24" s="22">
+        <v>31.52</v>
+      </c>
+      <c r="G24" s="21">
+        <f t="shared" si="3"/>
+        <v>-0.13308044077134984</v>
+      </c>
+      <c r="H24" s="20">
+        <f t="shared" si="4"/>
+        <v>45.375</v>
+      </c>
+      <c r="I24" s="20">
+        <f t="shared" si="5"/>
+        <v>33.396000000000001</v>
+      </c>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="19">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="E25" s="22">
+        <v>111.03400000000001</v>
+      </c>
+      <c r="F25" s="22">
+        <v>56</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="3"/>
+        <v>-0.49704998108687437</v>
+      </c>
+      <c r="H25" s="20">
+        <f t="shared" si="4"/>
+        <v>138.79250000000002</v>
+      </c>
+      <c r="I25" s="20">
+        <f t="shared" si="5"/>
+        <v>102.15128000000003</v>
+      </c>
+      <c r="J25" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="30">
-        <v>2.1749999999999998</v>
-      </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="31">
-        <v>-1.41E-2</v>
-      </c>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="23"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="16" t="s">
+      <c r="A27" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>48</v>
-      </c>
+      <c r="B27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="19">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="19">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="E28" s="23">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="F28" s="23">
-        <v>5.59</v>
-      </c>
-      <c r="G28" s="21">
-        <f t="shared" ref="G28:G32" si="3">IF(E28&gt;0,F28/E28-1.0014,(F28-E28))</f>
-        <v>-0.39902931034482758</v>
-      </c>
-      <c r="H28" s="20">
-        <f t="shared" ref="H28:H32" si="4">IF(E28&gt;0, IF(E28*1.25 &gt; F28,E28*1.25, IF(E28*1.25^2 &gt; F28,E28*1.25^2, IF(E28*1.25^3 &gt; F28,E28*1.25^3, IF(E28*1.25^4 &gt; F28,E28*1.25^4, IF(E28*1.25^5 &gt; F28,E28*1.25^5, IF(E28*1.25^6 &gt; F28,E28*1.25^6, IF(E28*1.25^7 &gt; F28, E28*1.25^7, IF(E28*1.25^8 &gt; F28, E28*1.25^8, IF(E28*1.25^9 &gt; F28, E28*1.25^9, E28*1.25^10))))))))),IF(1.25 &gt; F28-E28,1.25, IF(1.25^2 &gt; F28-E28,1.25^2, IF(1.25^3 &gt; F28-E28,1.25^3, IF(1.25^4 &gt; F28-E28,1.25^4, IF(1.25^5 &gt; F28-E28,1.25^5, IF(1.25^6 &gt; F28-E28,1.25^6, IF(1.25^7 &gt; F28-E28, 1.25^7, IF(1.25^8 &gt; F28-E28, 1.25^8, IF(1.25^9 &gt; F28-E28, 1.25^9, IF(1.25^10 &gt; F28-E28, 1.25^10, IF(1.25^11 &gt; F28-E28, 1.25^11, IF(1.25^12 &gt; F28-E28, 1.25^12, IF(1.25^13 &gt; F28-E28, 1.25^13, IF(1.25^14 &gt; F28-E28, 1.25^14, IF(1.25^15 &gt; F28-E28, 1.25^15, IF(1.25^16 &gt; F28-E28, 1.25^16, IF(1.25^17 &gt; F28-E28, 1.25^17, IF(1.25^18 &gt; F28-E28, 1.25^18, IF(1.25^19 &gt; F28-E28, 1.25^19, 1.25^20))))))))))))))))))))</f>
-        <v>11.6</v>
-      </c>
-      <c r="I28" s="20">
-        <f>H28/1.25*0.92</f>
-        <v>8.5375999999999994</v>
-      </c>
-      <c r="J28" s="20">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="19">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="19">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="E29" s="23">
-        <v>33.82</v>
-      </c>
-      <c r="F29" s="23">
-        <v>16.559999999999999</v>
-      </c>
-      <c r="G29" s="21">
-        <f t="shared" si="3"/>
-        <v>-0.51174890597279732</v>
-      </c>
-      <c r="H29" s="20">
-        <f t="shared" si="4"/>
-        <v>42.274999999999999</v>
-      </c>
-      <c r="I29" s="20">
-        <f t="shared" ref="I29:I32" si="5">H29/1.25*0.92</f>
-        <v>31.114400000000003</v>
-      </c>
-      <c r="J29" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="24">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="19">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="E30" s="23">
-        <v>22.58</v>
-      </c>
-      <c r="F30" s="23">
-        <v>23.97</v>
-      </c>
-      <c r="G30" s="21">
-        <f t="shared" si="3"/>
-        <v>6.0158901682905164E-2</v>
-      </c>
-      <c r="H30" s="20">
-        <f t="shared" si="4"/>
-        <v>28.224999999999998</v>
-      </c>
-      <c r="I30" s="20">
-        <f t="shared" si="5"/>
-        <v>20.773599999999998</v>
-      </c>
-      <c r="J30" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="33">
-        <v>2.76E-2</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="19">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="E31" s="23">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="F31" s="23">
-        <v>29</v>
-      </c>
-      <c r="G31" s="21">
-        <f t="shared" si="3"/>
-        <v>-0.20250192837465564</v>
-      </c>
-      <c r="H31" s="20">
-        <f t="shared" si="4"/>
-        <v>45.375</v>
-      </c>
-      <c r="I31" s="20">
-        <f t="shared" si="5"/>
-        <v>33.396000000000001</v>
-      </c>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="29"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="19">
-        <v>2.7E-2</v>
-      </c>
-      <c r="E32" s="23">
-        <v>111.03400000000001</v>
-      </c>
-      <c r="F32" s="23">
-        <v>52.8</v>
-      </c>
-      <c r="G32" s="21">
-        <f t="shared" si="3"/>
-        <v>-0.52586998216762448</v>
-      </c>
-      <c r="H32" s="20">
-        <f t="shared" si="4"/>
-        <v>138.79250000000002</v>
-      </c>
-      <c r="I32" s="20">
-        <f t="shared" si="5"/>
-        <v>102.15128000000003</v>
-      </c>
-      <c r="J32" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="8"/>
-      <c r="B33" s="25"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="16">
+        <v>23</v>
+      </c>
+      <c r="B29" s="16">
         <v>154004.837</v>
       </c>
-      <c r="C36" s="17">
-        <f>A2*B36</f>
-        <v>392404.32467599999</v>
+      <c r="C29" s="17">
+        <f>A2*B29</f>
+        <v>412116.94381200004</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A34:C34"/>
+  <mergeCells count="13">
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A19:J19"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="F11">
+  <conditionalFormatting sqref="F10">
     <cfRule type="cellIs" dxfId="7" priority="1" stopIfTrue="1" operator="lessThan">
-      <formula>$J$11</formula>
+      <formula>$J$10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F30">
+  <conditionalFormatting sqref="F23">
     <cfRule type="cellIs" dxfId="6" priority="15" stopIfTrue="1" operator="lessThan">
-      <formula>$J$30</formula>
+      <formula>$J$23</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G23 G28:G32">
+  <conditionalFormatting sqref="G22:G25 G7:G17">
     <cfRule type="cellIs" dxfId="5" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -2132,22 +1922,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H24">
+  <conditionalFormatting sqref="H7:H18">
     <cfRule type="cellIs" dxfId="3" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>E7*1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
+  <conditionalFormatting sqref="H22">
     <cfRule type="cellIs" dxfId="2" priority="6" stopIfTrue="1" operator="greaterThan">
-      <formula>E28*1.25</formula>
+      <formula>E22*1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29:H33">
+  <conditionalFormatting sqref="H23:H26">
     <cfRule type="cellIs" dxfId="1" priority="14" stopIfTrue="1" operator="greaterThan">
-      <formula>E29 * 1.25</formula>
+      <formula>E23 * 1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:J24 I28:J33">
+  <conditionalFormatting sqref="I22:J26 I7:J18">
     <cfRule type="cellIs" dxfId="0" priority="4" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/趋势投资.xlsx
+++ b/趋势投资.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08.ubuntu_ws\ediedone.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44387B60-F8EF-4007-B05E-E96EB4EEA4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCDB93B-BBBB-4E86-9400-CF0E94184510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{AED13B3B-36B7-4FA7-B5AB-20EFD3D048A6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>净值</t>
   </si>
@@ -47,27 +47,9 @@
     <t>食品饮料</t>
   </si>
   <si>
-    <t>洋河股份D</t>
-  </si>
-  <si>
     <t>房地产</t>
   </si>
   <si>
-    <t>绿城中国</t>
-  </si>
-  <si>
-    <t>银行</t>
-  </si>
-  <si>
-    <t>民生银行</t>
-  </si>
-  <si>
-    <t>软件服务</t>
-  </si>
-  <si>
-    <t>腾讯控股D</t>
-  </si>
-  <si>
     <t>交通运输</t>
   </si>
   <si>
@@ -77,16 +59,7 @@
     <t>公用事业</t>
   </si>
   <si>
-    <t>家用电器</t>
-  </si>
-  <si>
-    <t>美的集团</t>
-  </si>
-  <si>
     <t>旅游及消闲设施</t>
-  </si>
-  <si>
-    <t>澳博控股</t>
   </si>
   <si>
     <t>港股抄作业</t>
@@ -187,7 +160,11 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>洋河股份F</t>
+    <t>洋河股份</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>澳博控股</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -363,7 +340,7 @@
       <name val="Liberation Sans"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,8 +389,14 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -449,19 +432,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -570,7 +540,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -655,20 +625,29 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -676,13 +655,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -710,7 +683,7 @@
     <cellStyle name="Warning" xfId="21" xr:uid="{34E4EB9D-9B64-4F2F-AEC6-A63C04BE73F2}"/>
     <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FFCC0000"/>
@@ -799,19 +772,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFCCCC"/>
           <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006600"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFFCC"/>
-          <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1145,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2F0F4F-0A39-42ED-82E1-F32DA41D3C99}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="17.3984375" style="4" customWidth="1"/>
@@ -1159,29 +1119,29 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="16" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1">
-        <v>2.6760000000000002</v>
+        <v>2.71</v>
       </c>
       <c r="B2" s="2">
-        <v>5.0200000000000002E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="C2" s="3">
-        <v>171.52</v>
-      </c>
-      <c r="D2" s="25">
+        <v>175.6</v>
+      </c>
+      <c r="D2" s="38">
         <v>0.4052</v>
       </c>
     </row>
@@ -1191,69 +1151,69 @@
       <c r="C3" s="11"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
+      <c r="A4" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="28">
-        <v>2.8439999999999999</v>
-      </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
+      <c r="B5" s="33">
+        <v>2.903</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
       <c r="G5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="29">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
+      <c r="H5" s="34">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="J6" s="16" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1263,21 +1223,21 @@
       <c r="B7" s="27">
         <v>3.15E-2</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>48</v>
+      <c r="C7" s="26" t="s">
+        <v>39</v>
       </c>
       <c r="D7" s="19">
-        <v>2.18E-2</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="E7" s="20">
         <v>84.490300000000005</v>
       </c>
       <c r="F7" s="18">
-        <v>39.340000000000003</v>
+        <v>39.130000000000003</v>
       </c>
       <c r="G7" s="21">
-        <f t="shared" ref="G7:G17" si="0">IF(E7&gt;0,F7/E7-1.0014,(F7-E7))</f>
-        <v>-0.53578442046010022</v>
+        <f t="shared" ref="G7:G12" si="0">IF(E7&gt;0,F7/E7-1.0014,(F7-E7))</f>
+        <v>-0.53826991287757298</v>
       </c>
       <c r="H7" s="20">
         <f>IF(E7&gt;0, IF(E7*1.25 &gt; F7,E7*1.25, IF(E7*1.25^2 &gt; F7,E7*1.25^2, IF(E7*1.25^3 &gt; F7,E7*1.25^3, IF(E7*1.25^4 &gt; F7,E7*1.25^4, IF(E7*1.25^5 &gt; F7,E7*1.25^5, IF(E7*1.25^6 &gt; F7,E7*1.25^6, IF(E7*1.25^7 &gt; F7, E7*1.25^7, IF(E7*1.25^8 &gt; F7, E7*1.25^8, IF(E7*1.25^9 &gt; F7, E7*1.25^9, E7*1.25^10))))))))),IF(1.25 &gt; F7-E7,1.25, IF(1.25^2 &gt; F7-E7,1.25^2, IF(1.25^3 &gt; F7-E7,1.25^3, IF(1.25^4 &gt; F7-E7,1.25^4, IF(1.25^5 &gt; F7-E7,1.25^5, IF(1.25^6 &gt; F7-E7,1.25^6, IF(1.25^7 &gt; F7-E7, 1.25^7, IF(1.25^8 &gt; F7-E7, 1.25^8, IF(1.25^9 &gt; F7-E7, 1.25^9, IF(1.25^10 &gt; F7-E7, 1.25^10, IF(1.25^11 &gt; F7-E7, 1.25^11, IF(1.25^12 &gt; F7-E7, 1.25^12, IF(1.25^13 &gt; F7-E7, 1.25^13, IF(1.25^14 &gt; F7-E7, 1.25^14, IF(1.25^15 &gt; F7-E7, 1.25^15, IF(1.25^16 &gt; F7-E7, 1.25^16, IF(1.25^17 &gt; F7-E7, 1.25^17, IF(1.25^18 &gt; F7-E7, 1.25^18, IF(1.25^19 &gt; F7-E7, 1.25^19, 1.25^20))))))))))))))))))))</f>
@@ -1292,629 +1252,453 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="24" t="s">
+      <c r="A8" s="26" t="s">
         <v>3</v>
       </c>
+      <c r="B8" s="27">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>37</v>
+      </c>
       <c r="D8" s="19">
-        <v>9.7000000000000003E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="E8" s="20">
-        <v>152.2038</v>
+        <v>8.8960000000000008</v>
       </c>
       <c r="F8" s="18">
-        <v>39.340000000000003</v>
+        <v>0.52</v>
       </c>
       <c r="G8" s="21">
         <f t="shared" si="0"/>
-        <v>-0.74293076335807651</v>
+        <v>-0.94294676258992816</v>
       </c>
       <c r="H8" s="20">
-        <f t="shared" ref="H8:H17" si="1">IF(E8&gt;0, IF(E8*1.25 &gt; F8,E8*1.25, IF(E8*1.25^2 &gt; F8,E8*1.25^2, IF(E8*1.25^3 &gt; F8,E8*1.25^3, IF(E8*1.25^4 &gt; F8,E8*1.25^4, IF(E8*1.25^5 &gt; F8,E8*1.25^5, IF(E8*1.25^6 &gt; F8,E8*1.25^6, IF(E8*1.25^7 &gt; F8, E8*1.25^7, IF(E8*1.25^8 &gt; F8, E8*1.25^8, IF(E8*1.25^9 &gt; F8, E8*1.25^9, E8*1.25^10))))))))),IF(1.25 &gt; F8-E8,1.25, IF(1.25^2 &gt; F8-E8,1.25^2, IF(1.25^3 &gt; F8-E8,1.25^3, IF(1.25^4 &gt; F8-E8,1.25^4, IF(1.25^5 &gt; F8-E8,1.25^5, IF(1.25^6 &gt; F8-E8,1.25^6, IF(1.25^7 &gt; F8-E8, 1.25^7, IF(1.25^8 &gt; F8-E8, 1.25^8, IF(1.25^9 &gt; F8-E8, 1.25^9, IF(1.25^10 &gt; F8-E8, 1.25^10, IF(1.25^11 &gt; F8-E8, 1.25^11, IF(1.25^12 &gt; F8-E8, 1.25^12, IF(1.25^13 &gt; F8-E8, 1.25^13, IF(1.25^14 &gt; F8-E8, 1.25^14, IF(1.25^15 &gt; F8-E8, 1.25^15, IF(1.25^16 &gt; F8-E8, 1.25^16, IF(1.25^17 &gt; F8-E8, 1.25^17, IF(1.25^18 &gt; F8-E8, 1.25^18, IF(1.25^19 &gt; F8-E8, 1.25^19, 1.25^20))))))))))))))))))))</f>
-        <v>190.25475</v>
+        <f t="shared" ref="H8:H12" si="1">IF(E8&gt;0, IF(E8*1.25 &gt; F8,E8*1.25, IF(E8*1.25^2 &gt; F8,E8*1.25^2, IF(E8*1.25^3 &gt; F8,E8*1.25^3, IF(E8*1.25^4 &gt; F8,E8*1.25^4, IF(E8*1.25^5 &gt; F8,E8*1.25^5, IF(E8*1.25^6 &gt; F8,E8*1.25^6, IF(E8*1.25^7 &gt; F8, E8*1.25^7, IF(E8*1.25^8 &gt; F8, E8*1.25^8, IF(E8*1.25^9 &gt; F8, E8*1.25^9, E8*1.25^10))))))))),IF(1.25 &gt; F8-E8,1.25, IF(1.25^2 &gt; F8-E8,1.25^2, IF(1.25^3 &gt; F8-E8,1.25^3, IF(1.25^4 &gt; F8-E8,1.25^4, IF(1.25^5 &gt; F8-E8,1.25^5, IF(1.25^6 &gt; F8-E8,1.25^6, IF(1.25^7 &gt; F8-E8, 1.25^7, IF(1.25^8 &gt; F8-E8, 1.25^8, IF(1.25^9 &gt; F8-E8, 1.25^9, IF(1.25^10 &gt; F8-E8, 1.25^10, IF(1.25^11 &gt; F8-E8, 1.25^11, IF(1.25^12 &gt; F8-E8, 1.25^12, IF(1.25^13 &gt; F8-E8, 1.25^13, IF(1.25^14 &gt; F8-E8, 1.25^14, IF(1.25^15 &gt; F8-E8, 1.25^15, IF(1.25^16 &gt; F8-E8, 1.25^16, IF(1.25^17 &gt; F8-E8, 1.25^17, IF(1.25^18 &gt; F8-E8, 1.25^18, IF(1.25^19 &gt; F8-E8, 1.25^19, 1.25^20))))))))))))))))))))</f>
+        <v>11.120000000000001</v>
       </c>
       <c r="I8" s="20">
-        <f t="shared" ref="I8:I17" si="2">H8/1.25*0.92</f>
-        <v>140.02749600000001</v>
+        <f t="shared" ref="I8:I12" si="2">H8/1.25*0.92</f>
+        <v>8.1843200000000014</v>
       </c>
       <c r="J8" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="27">
-        <v>1.0200000000000001E-2</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>46</v>
+      <c r="B9" s="25">
+        <v>1.61E-2</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>5</v>
       </c>
       <c r="D9" s="19">
-        <v>8.9999999999999998E-4</v>
+        <v>1.5800000000000002E-2</v>
       </c>
       <c r="E9" s="20">
-        <v>8.8960000000000008</v>
+        <v>52.684100000000001</v>
       </c>
       <c r="F9" s="18">
-        <v>0.47499999999999998</v>
+        <v>23.65</v>
       </c>
       <c r="G9" s="21">
         <f t="shared" si="0"/>
-        <v>-0.94800521582733821</v>
+        <v>-0.55249795934636836</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="1"/>
-        <v>11.120000000000001</v>
+        <v>65.855125000000001</v>
       </c>
       <c r="I9" s="20">
         <f t="shared" si="2"/>
-        <v>8.1843200000000014</v>
+        <v>48.469372</v>
       </c>
       <c r="J9" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="24" t="s">
-        <v>5</v>
+      <c r="A10" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="25">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>36</v>
       </c>
       <c r="D10" s="19">
-        <v>9.2999999999999992E-3</v>
+        <v>3.4099999999999998E-2</v>
       </c>
       <c r="E10" s="20">
-        <v>9.5820000000000007</v>
+        <v>1.98</v>
       </c>
       <c r="F10" s="18">
-        <v>7</v>
+        <v>1.72</v>
       </c>
       <c r="G10" s="21">
         <f t="shared" si="0"/>
-        <v>-0.27086357754122325</v>
+        <v>-0.13271313131313134</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="1"/>
-        <v>11.977500000000001</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="I10" s="20">
         <f t="shared" si="2"/>
-        <v>8.8154400000000006</v>
+        <v>1.8216000000000001</v>
       </c>
       <c r="J10" s="20">
-        <v>8.8149999999999995</v>
+        <v>2.2770000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="25">
-        <v>7.7999999999999996E-3</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>7</v>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>40</v>
       </c>
       <c r="D11" s="19">
-        <v>7.7999999999999996E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="E11" s="20">
-        <v>5.1760000000000002</v>
+        <v>5.5410000000000004</v>
       </c>
       <c r="F11" s="18">
-        <v>3.5</v>
+        <v>1.405</v>
       </c>
       <c r="G11" s="21">
         <f t="shared" si="0"/>
-        <v>-0.32520216383307587</v>
+        <v>-0.74783566143295443</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="1"/>
-        <v>6.4700000000000006</v>
+        <v>6.9262500000000005</v>
       </c>
       <c r="I11" s="20">
         <f t="shared" si="2"/>
-        <v>4.7619199999999999</v>
+        <v>5.0977200000000007</v>
       </c>
       <c r="J11" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="37">
-        <v>0.19670000000000001</v>
-      </c>
-      <c r="C12" s="24" t="s">
+      <c r="B12" s="25">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="19">
-        <v>0.19670000000000001</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="E12" s="20">
-        <v>330</v>
+        <v>6.117</v>
       </c>
       <c r="F12" s="18">
-        <v>434.6</v>
+        <v>2.64</v>
       </c>
       <c r="G12" s="21">
         <f t="shared" si="0"/>
-        <v>0.31556969696969706</v>
+        <v>-0.56981589014222656</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="1"/>
-        <v>515.625</v>
+        <v>7.6462500000000002</v>
       </c>
       <c r="I12" s="20">
         <f t="shared" si="2"/>
-        <v>379.5</v>
+        <v>5.6276400000000004</v>
       </c>
       <c r="J12" s="20">
-        <v>379.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="25">
-        <v>1.61E-2</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="19">
-        <v>1.61E-2</v>
-      </c>
-      <c r="E13" s="20">
-        <v>52.684100000000001</v>
-      </c>
-      <c r="F13" s="18">
-        <v>23.7</v>
-      </c>
-      <c r="G13" s="21">
-        <f t="shared" si="0"/>
-        <v>-0.55154890640629728</v>
-      </c>
-      <c r="H13" s="20">
-        <f t="shared" si="1"/>
-        <v>65.855125000000001</v>
-      </c>
-      <c r="I13" s="20">
-        <f t="shared" si="2"/>
-        <v>48.469372</v>
-      </c>
-      <c r="J13" s="20">
+      <c r="A13" s="7"/>
+      <c r="B13" s="14"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="G13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="30"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="16" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="25">
-        <v>4.7600000000000003E-2</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="19">
-        <v>4.7600000000000003E-2</v>
-      </c>
-      <c r="E14" s="20">
-        <v>1.98</v>
-      </c>
-      <c r="F14" s="18">
-        <v>2.35</v>
-      </c>
-      <c r="G14" s="21">
-        <f t="shared" si="0"/>
-        <v>0.18546868686868678</v>
-      </c>
-      <c r="H14" s="20">
-        <f t="shared" si="1"/>
-        <v>2.4750000000000001</v>
-      </c>
-      <c r="I14" s="20">
-        <f t="shared" si="2"/>
-        <v>1.8216000000000001</v>
-      </c>
-      <c r="J14" s="20">
-        <v>2.2770000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="25">
-        <v>2.0799999999999999E-2</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="19">
-        <v>2.0799999999999999E-2</v>
-      </c>
-      <c r="E15" s="20">
-        <v>55.959800000000001</v>
-      </c>
-      <c r="F15" s="18">
-        <v>84.5</v>
-      </c>
-      <c r="G15" s="21">
-        <f t="shared" si="0"/>
-        <v>0.50861254471960216</v>
-      </c>
-      <c r="H15" s="20">
-        <f t="shared" si="1"/>
-        <v>87.437187500000007</v>
-      </c>
-      <c r="I15" s="20">
-        <f t="shared" si="2"/>
-        <v>64.353770000000011</v>
-      </c>
-      <c r="J15" s="20">
-        <v>68.724000000000004</v>
-      </c>
+      <c r="B15" s="35">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="34">
+        <v>-1.6999999999999999E-3</v>
+      </c>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="25">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="19">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="E16" s="20">
-        <v>5.5410000000000004</v>
-      </c>
-      <c r="F16" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="G16" s="21">
-        <f t="shared" si="0"/>
-        <v>-0.73069074174336768</v>
-      </c>
-      <c r="H16" s="20">
-        <f t="shared" si="1"/>
-        <v>6.9262500000000005</v>
-      </c>
-      <c r="I16" s="20">
-        <f t="shared" si="2"/>
-        <v>5.0977200000000007</v>
-      </c>
-      <c r="J16" s="20">
-        <v>0</v>
+      <c r="A16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="16" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B17" s="25">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>18</v>
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>11</v>
       </c>
       <c r="D17" s="19">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="E17" s="20">
-        <v>6.117</v>
-      </c>
-      <c r="F17" s="18">
-        <v>2.64</v>
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="E17" s="22">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="F17" s="22">
+        <v>5.66</v>
       </c>
       <c r="G17" s="21">
-        <f t="shared" si="0"/>
-        <v>-0.56981589014222656</v>
+        <f t="shared" ref="G17:G20" si="3">IF(E17&gt;0,F17/E17-1.0014,(F17-E17))</f>
+        <v>-0.39148620689655178</v>
       </c>
       <c r="H17" s="20">
-        <f t="shared" si="1"/>
-        <v>7.6462500000000002</v>
+        <f t="shared" ref="H17:H20" si="4">IF(E17&gt;0, IF(E17*1.25 &gt; F17,E17*1.25, IF(E17*1.25^2 &gt; F17,E17*1.25^2, IF(E17*1.25^3 &gt; F17,E17*1.25^3, IF(E17*1.25^4 &gt; F17,E17*1.25^4, IF(E17*1.25^5 &gt; F17,E17*1.25^5, IF(E17*1.25^6 &gt; F17,E17*1.25^6, IF(E17*1.25^7 &gt; F17, E17*1.25^7, IF(E17*1.25^8 &gt; F17, E17*1.25^8, IF(E17*1.25^9 &gt; F17, E17*1.25^9, E17*1.25^10))))))))),IF(1.25 &gt; F17-E17,1.25, IF(1.25^2 &gt; F17-E17,1.25^2, IF(1.25^3 &gt; F17-E17,1.25^3, IF(1.25^4 &gt; F17-E17,1.25^4, IF(1.25^5 &gt; F17-E17,1.25^5, IF(1.25^6 &gt; F17-E17,1.25^6, IF(1.25^7 &gt; F17-E17, 1.25^7, IF(1.25^8 &gt; F17-E17, 1.25^8, IF(1.25^9 &gt; F17-E17, 1.25^9, IF(1.25^10 &gt; F17-E17, 1.25^10, IF(1.25^11 &gt; F17-E17, 1.25^11, IF(1.25^12 &gt; F17-E17, 1.25^12, IF(1.25^13 &gt; F17-E17, 1.25^13, IF(1.25^14 &gt; F17-E17, 1.25^14, IF(1.25^15 &gt; F17-E17, 1.25^15, IF(1.25^16 &gt; F17-E17, 1.25^16, IF(1.25^17 &gt; F17-E17, 1.25^17, IF(1.25^18 &gt; F17-E17, 1.25^18, IF(1.25^19 &gt; F17-E17, 1.25^19, 1.25^20))))))))))))))))))))</f>
+        <v>11.6</v>
       </c>
       <c r="I17" s="20">
-        <f t="shared" si="2"/>
-        <v>5.6276400000000004</v>
+        <f>H17/1.25*0.92</f>
+        <v>8.5375999999999994</v>
       </c>
       <c r="J17" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="7"/>
-      <c r="B18" s="14"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="G18"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="32"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="33">
-        <v>2.2240000000000002</v>
-      </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="29">
-        <v>2.23E-2</v>
-      </c>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" s="18" t="s">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="25">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="25">
-        <v>1.7899999999999999E-2</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="19">
-        <v>1.7899999999999999E-2</v>
-      </c>
-      <c r="E22" s="22">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="F22" s="22">
-        <v>5.88</v>
-      </c>
-      <c r="G22" s="21">
-        <f t="shared" ref="G22:G25" si="3">IF(E22&gt;0,F22/E22-1.0014,(F22-E22))</f>
-        <v>-0.36777931034482758</v>
-      </c>
-      <c r="H22" s="20">
-        <f t="shared" ref="H22:H25" si="4">IF(E22&gt;0, IF(E22*1.25 &gt; F22,E22*1.25, IF(E22*1.25^2 &gt; F22,E22*1.25^2, IF(E22*1.25^3 &gt; F22,E22*1.25^3, IF(E22*1.25^4 &gt; F22,E22*1.25^4, IF(E22*1.25^5 &gt; F22,E22*1.25^5, IF(E22*1.25^6 &gt; F22,E22*1.25^6, IF(E22*1.25^7 &gt; F22, E22*1.25^7, IF(E22*1.25^8 &gt; F22, E22*1.25^8, IF(E22*1.25^9 &gt; F22, E22*1.25^9, E22*1.25^10))))))))),IF(1.25 &gt; F22-E22,1.25, IF(1.25^2 &gt; F22-E22,1.25^2, IF(1.25^3 &gt; F22-E22,1.25^3, IF(1.25^4 &gt; F22-E22,1.25^4, IF(1.25^5 &gt; F22-E22,1.25^5, IF(1.25^6 &gt; F22-E22,1.25^6, IF(1.25^7 &gt; F22-E22, 1.25^7, IF(1.25^8 &gt; F22-E22, 1.25^8, IF(1.25^9 &gt; F22-E22, 1.25^9, IF(1.25^10 &gt; F22-E22, 1.25^10, IF(1.25^11 &gt; F22-E22, 1.25^11, IF(1.25^12 &gt; F22-E22, 1.25^12, IF(1.25^13 &gt; F22-E22, 1.25^13, IF(1.25^14 &gt; F22-E22, 1.25^14, IF(1.25^15 &gt; F22-E22, 1.25^15, IF(1.25^16 &gt; F22-E22, 1.25^16, IF(1.25^17 &gt; F22-E22, 1.25^17, IF(1.25^18 &gt; F22-E22, 1.25^18, IF(1.25^19 &gt; F22-E22, 1.25^19, 1.25^20))))))))))))))))))))</f>
-        <v>11.6</v>
-      </c>
-      <c r="I22" s="20">
-        <f>H22/1.25*0.92</f>
-        <v>8.5375999999999994</v>
-      </c>
-      <c r="J22" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="25">
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="19">
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="E23" s="22">
+      <c r="D18" s="19">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="E18" s="22">
         <v>22.58</v>
       </c>
-      <c r="F23" s="22">
-        <v>26.24</v>
-      </c>
-      <c r="G23" s="21">
+      <c r="F18" s="22">
+        <v>26.31</v>
+      </c>
+      <c r="G18" s="21">
         <f t="shared" si="3"/>
-        <v>0.16069034543844096</v>
-      </c>
-      <c r="H23" s="20">
+        <v>0.16379043401240034</v>
+      </c>
+      <c r="H18" s="20">
         <f t="shared" si="4"/>
         <v>28.224999999999998</v>
       </c>
-      <c r="I23" s="20">
-        <f t="shared" ref="I23:I25" si="5">H23/1.25*0.92</f>
+      <c r="I18" s="20">
+        <f t="shared" ref="I18:I20" si="5">H18/1.25*0.92</f>
         <v>20.773599999999998</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J18" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="27">
+    <row r="19" spans="1:10">
+      <c r="A19" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="32">
         <v>3.5099999999999999E-2</v>
       </c>
-      <c r="C24" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="19">
+      <c r="C19" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="19">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E19" s="22">
         <v>36.299999999999997</v>
       </c>
-      <c r="F24" s="22">
-        <v>31.52</v>
-      </c>
-      <c r="G24" s="21">
+      <c r="F19" s="22">
+        <v>28.68</v>
+      </c>
+      <c r="G19" s="21">
         <f t="shared" si="3"/>
-        <v>-0.13308044077134984</v>
-      </c>
-      <c r="H24" s="20">
+        <v>-0.21131735537190088</v>
+      </c>
+      <c r="H19" s="20">
         <f t="shared" si="4"/>
         <v>45.375</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I19" s="20">
         <f t="shared" si="5"/>
         <v>33.396000000000001</v>
       </c>
-      <c r="J24" s="20"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="19">
-        <v>3.4299999999999997E-2</v>
-      </c>
-      <c r="E25" s="22">
-        <v>111.03400000000001</v>
-      </c>
-      <c r="F25" s="22">
-        <v>56</v>
-      </c>
-      <c r="G25" s="21">
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="31"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="19">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="E20" s="22">
+        <v>100.77</v>
+      </c>
+      <c r="F20" s="22">
+        <v>56.86</v>
+      </c>
+      <c r="G20" s="21">
         <f t="shared" si="3"/>
-        <v>-0.49704998108687437</v>
-      </c>
-      <c r="H25" s="20">
+        <v>-0.43714476530713509</v>
+      </c>
+      <c r="H20" s="20">
         <f t="shared" si="4"/>
-        <v>138.79250000000002</v>
-      </c>
-      <c r="I25" s="20">
+        <v>125.96249999999999</v>
+      </c>
+      <c r="I20" s="20">
         <f t="shared" si="5"/>
-        <v>102.15128000000003</v>
-      </c>
-      <c r="J25" s="20">
+        <v>92.708399999999997</v>
+      </c>
+      <c r="J20" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="8"/>
-      <c r="B26" s="23"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="16" t="s">
+    <row r="21" spans="1:10">
+      <c r="A21" s="8"/>
+      <c r="B21" s="23"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="28" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="16">
+      <c r="B22" s="29"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="16">
         <v>154004.837</v>
       </c>
-      <c r="C29" s="17">
-        <f>A2*B29</f>
-        <v>412116.94381200004</v>
+      <c r="C24" s="17">
+        <f>A2*B24</f>
+        <v>417353.10826999997</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
+  <mergeCells count="9">
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A14:J14"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="H5:J5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A19:J19"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="cellIs" dxfId="7" priority="1" stopIfTrue="1" operator="lessThan">
-      <formula>$J$10</formula>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="cellIs" dxfId="6" priority="15" stopIfTrue="1" operator="lessThan">
+      <formula>$J$18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="cellIs" dxfId="6" priority="15" stopIfTrue="1" operator="lessThan">
-      <formula>$J$23</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G25 G7:G17">
+  <conditionalFormatting sqref="G17:G20 G7:G12">
     <cfRule type="cellIs" dxfId="5" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -1922,22 +1706,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H18">
+  <conditionalFormatting sqref="H7:H13">
     <cfRule type="cellIs" dxfId="3" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>E7*1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
+  <conditionalFormatting sqref="H17">
     <cfRule type="cellIs" dxfId="2" priority="6" stopIfTrue="1" operator="greaterThan">
-      <formula>E22*1.25</formula>
+      <formula>E17*1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23:H26">
+  <conditionalFormatting sqref="H18:H21">
     <cfRule type="cellIs" dxfId="1" priority="14" stopIfTrue="1" operator="greaterThan">
-      <formula>E23 * 1.25</formula>
+      <formula>E18 * 1.25</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22:J26 I7:J18">
+  <conditionalFormatting sqref="I17:J21 I7:J13">
     <cfRule type="cellIs" dxfId="0" priority="4" stopIfTrue="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
